--- a/7-TESLA_500G_Calibration/barns.xlsx
+++ b/7-TESLA_500G_Calibration/barns.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmathew\cernbox\WINDOWS\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmathew\cernbox\WINDOWS\Desktop\Git-Projects\HEP-Pheno-Project\7-TESLA_500G_Calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C8402D-1705-4A63-91E2-468CE7C36CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95387CD2-7B05-46C9-A2B8-0B22382E8326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{7960ABCD-F717-4580-A97E-BFEE89018374}"/>
   </bookViews>
@@ -106,12 +106,42 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -141,24 +171,54 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -529,147 +589,147 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="15">
         <v>91.2</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15">
         <v>160</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3">
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15">
         <v>240</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3">
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15">
         <v>365</v>
       </c>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3">
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="15"/>
+      <c r="Z5" s="15">
         <v>500</v>
       </c>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
+      <c r="AA5" s="15"/>
+      <c r="AB5" s="15"/>
+      <c r="AC5" s="15"/>
+      <c r="AD5" s="15"/>
+      <c r="AE5" s="15"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="P6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="Q6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="R6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="S6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="T6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="U6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="V6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="W6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="X6" s="2" t="s">
+      <c r="X6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Y6" s="2" t="s">
+      <c r="Y6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="Z6" s="2" t="s">
+      <c r="Z6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA6" s="2" t="s">
+      <c r="AA6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AB6" s="2" t="s">
+      <c r="AB6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="AC6" s="2" t="s">
+      <c r="AC6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="2" t="s">
+      <c r="AD6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="AE6" s="2" t="s">
+      <c r="AE6" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="4">
@@ -679,18 +739,18 @@
         <f>B7*G7/F7</f>
         <v>13.096722450000001</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="7">
         <v>569045</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="8">
         <f>D7*G7/F7</f>
         <v>17.293277549999999</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="10">
         <f>B7+D7</f>
         <v>1000000</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="11">
         <v>30.39</v>
       </c>
       <c r="H7" s="4">
@@ -700,18 +760,18 @@
         <f>H7*M$7/L$7</f>
         <v>11.295126</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="7">
         <v>925885</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="8">
         <f>J7*M$7/L$7</f>
         <v>141.104874</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="10">
         <f>H7+J7</f>
         <v>1000000</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="11">
         <v>152.4</v>
       </c>
       <c r="N7" s="4">
@@ -721,18 +781,18 @@
         <f>N7*S$7/R$7</f>
         <v>5.8524165000000004</v>
       </c>
-      <c r="P7" s="4">
+      <c r="P7" s="7">
         <v>902945</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="Q7" s="8">
         <f>P7*S$7/R$7</f>
         <v>54.4475835</v>
       </c>
-      <c r="R7" s="4">
+      <c r="R7" s="10">
         <f>N7+P7</f>
         <v>1000000</v>
       </c>
-      <c r="S7" s="5">
+      <c r="S7" s="11">
         <v>60.3</v>
       </c>
       <c r="T7" s="4">
@@ -742,18 +802,18 @@
         <f>T7*Y$7/X$7</f>
         <v>2.7538214999999999</v>
       </c>
-      <c r="V7" s="4">
+      <c r="V7" s="7">
         <v>897475</v>
       </c>
-      <c r="W7" s="5">
+      <c r="W7" s="8">
         <f>V7*Y$7/X$7</f>
         <v>24.106178499999999</v>
       </c>
-      <c r="X7" s="4">
+      <c r="X7" s="10">
         <f>T7+V7</f>
         <v>1000000</v>
       </c>
-      <c r="Y7" s="5">
+      <c r="Y7" s="11">
         <v>26.86</v>
       </c>
       <c r="Z7" s="4">
@@ -763,44 +823,44 @@
         <f>Z7*AE$7/AD$7</f>
         <v>1.6120263000000001</v>
       </c>
-      <c r="AB7" s="4">
+      <c r="AB7" s="7">
         <v>894982</v>
       </c>
-      <c r="AC7" s="5">
+      <c r="AC7" s="8">
         <f>AB7*AE$7/AD$7</f>
         <v>13.7379737</v>
       </c>
-      <c r="AD7" s="4">
-        <f>Z7+AB7</f>
+      <c r="AD7" s="10">
+        <f t="shared" ref="AD7:AD13" si="0">Z7+AB7</f>
         <v>1000000</v>
       </c>
-      <c r="AE7" s="5">
+      <c r="AE7" s="11">
         <v>15.35</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="4">
         <v>430955</v>
       </c>
       <c r="C8" s="5">
-        <f t="shared" ref="C8" si="0">B8*G8/F8</f>
+        <f t="shared" ref="C8" si="1">B8*G8/F8</f>
         <v>13.096722450000001</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="7">
         <v>569045</v>
       </c>
-      <c r="E8" s="5">
-        <f t="shared" ref="E8" si="1">D8*G8/F8</f>
+      <c r="E8" s="8">
+        <f t="shared" ref="E8" si="2">D8*G8/F8</f>
         <v>17.293277549999999</v>
       </c>
-      <c r="F8" s="4">
-        <f t="shared" ref="F8" si="2">B8+D8</f>
+      <c r="F8" s="10">
+        <f t="shared" ref="F8" si="3">B8+D8</f>
         <v>1000000</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="11">
         <f>F8*G7/F7</f>
         <v>30.39</v>
       </c>
@@ -808,21 +868,21 @@
         <v>70832</v>
       </c>
       <c r="I8" s="5">
-        <f t="shared" ref="I8:I11" si="3">H8*M$7/L$7</f>
+        <f t="shared" ref="I8:I11" si="4">H8*M$7/L$7</f>
         <v>10.7947968</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="7">
         <v>921081</v>
       </c>
-      <c r="K8" s="5">
-        <f t="shared" ref="K8:K11" si="4">J8*M$7/L$7</f>
+      <c r="K8" s="8">
+        <f t="shared" ref="K8:K11" si="5">J8*M$7/L$7</f>
         <v>140.37274440000002</v>
       </c>
-      <c r="L8" s="4">
-        <f t="shared" ref="L8:L11" si="5">H8+J8</f>
+      <c r="L8" s="10">
+        <f t="shared" ref="L8:L11" si="6">H8+J8</f>
         <v>991913</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="11">
         <f>L8*M$7/L$7</f>
         <v>151.16754120000002</v>
       </c>
@@ -830,21 +890,21 @@
         <v>57323</v>
       </c>
       <c r="O8" s="5">
-        <f t="shared" ref="O8:O11" si="6">N8*S$7/R$7</f>
+        <f t="shared" ref="O8:O11" si="7">N8*S$7/R$7</f>
         <v>3.4565769</v>
       </c>
-      <c r="P8" s="4">
+      <c r="P8" s="7">
         <v>806303</v>
       </c>
-      <c r="Q8" s="5">
-        <f t="shared" ref="Q8:Q11" si="7">P8*S$7/R$7</f>
+      <c r="Q8" s="8">
+        <f t="shared" ref="Q8:Q11" si="8">P8*S$7/R$7</f>
         <v>48.620070900000002</v>
       </c>
-      <c r="R8" s="4">
-        <f t="shared" ref="R8:R11" si="8">N8+P8</f>
+      <c r="R8" s="10">
+        <f t="shared" ref="R8:R11" si="9">N8+P8</f>
         <v>863626</v>
       </c>
-      <c r="S8" s="5">
+      <c r="S8" s="11">
         <f>R8*S$7/R$7</f>
         <v>52.076647799999996</v>
       </c>
@@ -852,21 +912,21 @@
         <v>46173</v>
       </c>
       <c r="U8" s="5">
-        <f t="shared" ref="U8:U11" si="9">T8*Y$7/X$7</f>
+        <f t="shared" ref="U8:U11" si="10">T8*Y$7/X$7</f>
         <v>1.2402067800000001</v>
       </c>
-      <c r="V8" s="4">
+      <c r="V8" s="7">
         <v>738467</v>
       </c>
-      <c r="W8" s="5">
-        <f t="shared" ref="W8:W11" si="10">V8*Y$7/X$7</f>
+      <c r="W8" s="8">
+        <f t="shared" ref="W8:W11" si="11">V8*Y$7/X$7</f>
         <v>19.835223620000001</v>
       </c>
-      <c r="X8" s="4">
-        <f t="shared" ref="X8:X11" si="11">T8+V8</f>
+      <c r="X8" s="10">
+        <f t="shared" ref="X8:X11" si="12">T8+V8</f>
         <v>784640</v>
       </c>
-      <c r="Y8" s="5">
+      <c r="Y8" s="11">
         <f>X8*Y$7/X$7</f>
         <v>21.075430399999998</v>
       </c>
@@ -874,37 +934,35 @@
         <v>39617</v>
       </c>
       <c r="AA8" s="5">
-        <f t="shared" ref="AA8:AA11" si="12">Z8*AE$7/AD$7</f>
+        <f t="shared" ref="AA8:AA11" si="13">Z8*AE$7/AD$7</f>
         <v>0.60812094999999999</v>
       </c>
-      <c r="AB8" s="4">
+      <c r="AB8" s="7">
         <v>687761</v>
       </c>
-      <c r="AC8" s="5">
-        <f t="shared" ref="AC8:AC11" si="13">AB8*AE$7/AD$7</f>
+      <c r="AC8" s="8">
+        <f t="shared" ref="AC8:AC11" si="14">AB8*AE$7/AD$7</f>
         <v>10.557131349999999</v>
       </c>
-      <c r="AD8" s="4">
-        <f>Z8+AB8</f>
+      <c r="AD8" s="10">
+        <f t="shared" si="0"/>
         <v>727378</v>
       </c>
-      <c r="AE8" s="7">
+      <c r="AE8" s="12">
         <f>AD8*AE$7/AD$7</f>
         <v>11.165252299999999</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="4">
-        <v>0</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="5"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="17"/>
       <c r="H9" s="4">
         <v>2843</v>
       </c>
@@ -912,18 +970,18 @@
         <f>H9*M$7/L$7</f>
         <v>0.43327320000000002</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="7">
         <v>3941</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="8">
         <f>J9*M$7/L$7</f>
         <v>0.60060840000000004</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="10">
         <f>H9+J9</f>
         <v>6784</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="11">
         <f>L9*M$7/L$7</f>
         <v>1.0338816000000002</v>
       </c>
@@ -934,18 +992,18 @@
         <f>N9*S$7/R$7</f>
         <v>2.1810510000000001</v>
       </c>
-      <c r="P9" s="4">
+      <c r="P9" s="7">
         <v>88073</v>
       </c>
-      <c r="Q9" s="5">
+      <c r="Q9" s="8">
         <f>P9*S$7/R$7</f>
         <v>5.3108018999999995</v>
       </c>
-      <c r="R9" s="4">
+      <c r="R9" s="10">
         <f>N9+P9</f>
         <v>124243</v>
       </c>
-      <c r="S9" s="5">
+      <c r="S9" s="11">
         <f>R9*S$7/R$7</f>
         <v>7.4918528999999996</v>
       </c>
@@ -956,18 +1014,18 @@
         <f>T9*Y$7/X$7</f>
         <v>1.3359895400000001</v>
       </c>
-      <c r="V9" s="4">
+      <c r="V9" s="7">
         <v>140943</v>
       </c>
-      <c r="W9" s="5">
+      <c r="W9" s="8">
         <f>V9*Y$7/X$7</f>
         <v>3.78572898</v>
       </c>
-      <c r="X9" s="4">
+      <c r="X9" s="10">
         <f>T9+V9</f>
         <v>190682</v>
       </c>
-      <c r="Y9" s="5">
+      <c r="Y9" s="11">
         <f>X9*Y$7/X$7</f>
         <v>5.1217185199999999</v>
       </c>
@@ -978,242 +1036,236 @@
         <f>Z9*AE$7/AD$7</f>
         <v>0.86243974999999995</v>
       </c>
-      <c r="AB9" s="4">
+      <c r="AB9" s="7">
         <v>176832</v>
       </c>
-      <c r="AC9" s="5">
+      <c r="AC9" s="8">
         <f>AB9*AE$7/AD$7</f>
         <v>2.7143711999999995</v>
       </c>
-      <c r="AD9" s="4">
-        <f>Z9+AB9</f>
+      <c r="AD9" s="10">
+        <f t="shared" si="0"/>
         <v>233017</v>
       </c>
-      <c r="AE9" s="7">
+      <c r="AE9" s="12">
         <f>AD9*AE$7/AD$7</f>
         <v>3.5768109499999996</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="4">
-        <v>0</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="5"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17"/>
       <c r="H10" s="4">
         <v>439</v>
       </c>
       <c r="I10" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.6903600000000008E-2</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="7">
         <v>862</v>
       </c>
-      <c r="K10" s="5">
-        <f t="shared" si="4"/>
+      <c r="K10" s="8">
+        <f t="shared" si="5"/>
         <v>0.13136880000000001</v>
       </c>
-      <c r="L10" s="4">
-        <f t="shared" si="5"/>
+      <c r="L10" s="10">
+        <f t="shared" si="6"/>
         <v>1301</v>
       </c>
-      <c r="M10" s="5">
-        <f t="shared" ref="M10:M11" si="14">L10*M$7/L$7</f>
+      <c r="M10" s="11">
+        <f t="shared" ref="M10:M11" si="15">L10*M$7/L$7</f>
         <v>0.19827239999999999</v>
       </c>
       <c r="N10" s="4">
         <v>3134</v>
       </c>
       <c r="O10" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.18898019999999999</v>
       </c>
-      <c r="P10" s="4">
+      <c r="P10" s="7">
         <v>7531</v>
       </c>
-      <c r="Q10" s="5">
-        <f t="shared" si="7"/>
+      <c r="Q10" s="8">
+        <f t="shared" si="8"/>
         <v>0.4541193</v>
       </c>
-      <c r="R10" s="4">
-        <f t="shared" si="8"/>
+      <c r="R10" s="10">
+        <f t="shared" si="9"/>
         <v>10665</v>
       </c>
-      <c r="S10" s="5">
-        <f t="shared" ref="S10:S11" si="15">R10*S$7/R$7</f>
+      <c r="S10" s="11">
+        <f t="shared" ref="S10:S11" si="16">R10*S$7/R$7</f>
         <v>0.64309950000000005</v>
       </c>
       <c r="T10" s="4">
         <v>3892</v>
       </c>
       <c r="U10" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.10453912</v>
       </c>
-      <c r="V10" s="4">
+      <c r="V10" s="7">
         <v>11138</v>
       </c>
-      <c r="W10" s="5">
-        <f t="shared" si="10"/>
+      <c r="W10" s="8">
+        <f t="shared" si="11"/>
         <v>0.29916668000000002</v>
       </c>
-      <c r="X10" s="4">
-        <f t="shared" si="11"/>
+      <c r="X10" s="10">
+        <f t="shared" si="12"/>
         <v>15030</v>
       </c>
-      <c r="Y10" s="5">
-        <f t="shared" ref="Y10:Y11" si="16">X10*Y$7/X$7</f>
+      <c r="Y10" s="11">
+        <f t="shared" ref="Y10:Y11" si="17">X10*Y$7/X$7</f>
         <v>0.4037058</v>
       </c>
       <c r="Z10" s="4">
         <v>4226</v>
       </c>
       <c r="AA10" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.4869099999999999E-2</v>
       </c>
-      <c r="AB10" s="4">
+      <c r="AB10" s="7">
         <v>13361</v>
       </c>
-      <c r="AC10" s="5">
-        <f t="shared" si="13"/>
+      <c r="AC10" s="8">
+        <f t="shared" si="14"/>
         <v>0.20509135000000001</v>
       </c>
-      <c r="AD10" s="4">
-        <f>Z10+AB10</f>
+      <c r="AD10" s="10">
+        <f t="shared" si="0"/>
         <v>17587</v>
       </c>
-      <c r="AE10" s="7">
-        <f t="shared" ref="AE10:AE11" si="17">AD10*AE$7/AD$7</f>
+      <c r="AE10" s="12">
+        <f t="shared" ref="AE10:AE11" si="18">AD10*AE$7/AD$7</f>
         <v>0.26996045000000002</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="4">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="5"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17"/>
       <c r="H11" s="4">
         <v>1</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" si="3"/>
-        <v>1.5240000000000002E-4</v>
-      </c>
-      <c r="J11" s="4">
-        <v>1</v>
-      </c>
-      <c r="K11" s="5">
         <f t="shared" si="4"/>
         <v>1.5240000000000002E-4</v>
       </c>
-      <c r="L11" s="4">
+      <c r="J11" s="7">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8">
         <f t="shared" si="5"/>
+        <v>1.5240000000000002E-4</v>
+      </c>
+      <c r="L11" s="10">
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="M11" s="5">
-        <f t="shared" si="14"/>
+      <c r="M11" s="11">
+        <f t="shared" si="15"/>
         <v>3.0480000000000004E-4</v>
       </c>
       <c r="N11" s="4">
         <v>15</v>
       </c>
       <c r="O11" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.0450000000000003E-4</v>
       </c>
-      <c r="P11" s="4">
+      <c r="P11" s="7">
         <v>44</v>
       </c>
-      <c r="Q11" s="5">
-        <f t="shared" si="7"/>
+      <c r="Q11" s="8">
+        <f t="shared" si="8"/>
         <v>2.6531999999999997E-3</v>
       </c>
-      <c r="R11" s="4">
-        <f t="shared" si="8"/>
+      <c r="R11" s="10">
+        <f t="shared" si="9"/>
         <v>59</v>
       </c>
-      <c r="S11" s="5">
-        <f t="shared" si="15"/>
+      <c r="S11" s="11">
+        <f t="shared" si="16"/>
         <v>3.5577E-3</v>
       </c>
       <c r="T11" s="4">
         <v>208</v>
       </c>
       <c r="U11" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.5868799999999998E-3</v>
       </c>
-      <c r="V11" s="4">
+      <c r="V11" s="7">
         <v>517</v>
       </c>
-      <c r="W11" s="5">
-        <f t="shared" si="10"/>
+      <c r="W11" s="8">
+        <f t="shared" si="11"/>
         <v>1.3886619999999999E-2</v>
       </c>
-      <c r="X11" s="4">
-        <f t="shared" si="11"/>
+      <c r="X11" s="10">
+        <f t="shared" si="12"/>
         <v>725</v>
       </c>
-      <c r="Y11" s="5">
-        <f t="shared" si="16"/>
+      <c r="Y11" s="11">
+        <f t="shared" si="17"/>
         <v>1.9473500000000001E-2</v>
       </c>
       <c r="Z11" s="4">
         <v>752</v>
       </c>
       <c r="AA11" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.1543199999999998E-2</v>
       </c>
-      <c r="AB11" s="4">
+      <c r="AB11" s="7">
         <v>2005</v>
       </c>
-      <c r="AC11" s="5">
-        <f t="shared" si="13"/>
+      <c r="AC11" s="8">
+        <f t="shared" si="14"/>
         <v>3.0776749999999999E-2</v>
       </c>
-      <c r="AD11" s="4">
-        <f>Z11+AB11</f>
+      <c r="AD11" s="10">
+        <f t="shared" si="0"/>
         <v>2757</v>
       </c>
-      <c r="AE11" s="7">
-        <f t="shared" si="17"/>
+      <c r="AE11" s="12">
+        <f t="shared" si="18"/>
         <v>4.2319949999999995E-2</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="4">
-        <v>0</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="5"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="17"/>
       <c r="N12" s="4">
         <v>413</v>
       </c>
@@ -1221,18 +1273,18 @@
         <f>N12*S$7/R$7</f>
         <v>2.4903899999999996E-2</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P12" s="7">
         <v>994</v>
       </c>
-      <c r="Q12" s="5">
+      <c r="Q12" s="8">
         <f>P12*S$7/R$7</f>
         <v>5.9938199999999997E-2</v>
       </c>
-      <c r="R12" s="4">
+      <c r="R12" s="10">
         <f>N12+P12</f>
         <v>1407</v>
       </c>
-      <c r="S12" s="5">
+      <c r="S12" s="11">
         <f>R12*S$7/R$7</f>
         <v>8.484209999999999E-2</v>
       </c>
@@ -1243,18 +1295,18 @@
         <f>T12*Y$7/X$7</f>
         <v>1.364488E-2</v>
       </c>
-      <c r="V12" s="4">
+      <c r="V12" s="7">
         <v>1601</v>
       </c>
-      <c r="W12" s="5">
+      <c r="W12" s="8">
         <f>V12*Y$7/X$7</f>
         <v>4.3002860000000004E-2</v>
       </c>
-      <c r="X12" s="4">
+      <c r="X12" s="10">
         <f>T12+V12</f>
         <v>2109</v>
       </c>
-      <c r="Y12" s="5">
+      <c r="Y12" s="11">
         <f>X12*Y$7/X$7</f>
         <v>5.6647739999999995E-2</v>
       </c>
@@ -1265,46 +1317,44 @@
         <f>Z12*AE$7/AD$7</f>
         <v>6.0632500000000001E-3</v>
       </c>
-      <c r="AB12" s="4">
+      <c r="AB12" s="7">
         <v>1516</v>
       </c>
-      <c r="AC12" s="5">
+      <c r="AC12" s="8">
         <f>AB12*AE$7/AD$7</f>
         <v>2.3270599999999999E-2</v>
       </c>
-      <c r="AD12" s="4">
-        <f>Z12+AB12</f>
+      <c r="AD12" s="10">
+        <f t="shared" si="0"/>
         <v>1911</v>
       </c>
-      <c r="AE12" s="7">
+      <c r="AE12" s="12">
         <f>AD12*AE$7/AD$7</f>
         <v>2.9333849999999998E-2</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="4">
-        <v>0</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="5"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="17"/>
       <c r="T13" s="4">
         <v>2005</v>
       </c>
@@ -1312,18 +1362,18 @@
         <f>T13*Y$7/X$7</f>
         <v>5.3854299999999994E-2</v>
       </c>
-      <c r="V13" s="4">
+      <c r="V13" s="7">
         <v>4809</v>
       </c>
-      <c r="W13" s="5">
+      <c r="W13" s="8">
         <f>V13*Y$7/X$7</f>
         <v>0.12916973999999998</v>
       </c>
-      <c r="X13" s="4">
+      <c r="X13" s="10">
         <f>T13+V13</f>
         <v>6814</v>
       </c>
-      <c r="Y13" s="5">
+      <c r="Y13" s="11">
         <f>X13*Y$7/X$7</f>
         <v>0.18302404</v>
       </c>
@@ -1334,24 +1384,24 @@
         <f>Z13*AE$7/AD$7</f>
         <v>5.8990049999999995E-2</v>
       </c>
-      <c r="AB13" s="4">
+      <c r="AB13" s="7">
         <v>13507</v>
       </c>
-      <c r="AC13" s="5">
+      <c r="AC13" s="8">
         <f>AB13*AE$7/AD$7</f>
         <v>0.20733244999999997</v>
       </c>
-      <c r="AD13" s="4">
-        <f>Z13+AB13</f>
+      <c r="AD13" s="10">
+        <f t="shared" si="0"/>
         <v>17350</v>
       </c>
-      <c r="AE13" s="7">
+      <c r="AE13" s="12">
         <f>AD13*AE$7/AD$7</f>
         <v>0.26632250000000002</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="Y14" s="6"/>
+      <c r="Y14" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/7-TESLA_500G_Calibration/barns.xlsx
+++ b/7-TESLA_500G_Calibration/barns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmathew\cernbox\WINDOWS\Desktop\Git-Projects\HEP-Pheno-Project\7-TESLA_500G_Calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95387CD2-7B05-46C9-A2B8-0B22382E8326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC750869-B72E-4DC5-97C2-1452CAA80AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{7960ABCD-F717-4580-A97E-BFEE89018374}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{7960ABCD-F717-4580-A97E-BFEE89018374}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="15">
   <si>
     <t>al</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>σ (pb)</t>
+  </si>
+  <si>
+    <t>Non+Rad</t>
   </si>
 </sst>
 </file>
@@ -211,14 +214,14 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -554,19 +557,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8C8F55F-93F0-4A61-B4C8-B8A5CBE0D442}">
-  <dimension ref="A5:AE14"/>
+  <dimension ref="A5:AE22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
-    <col min="4" max="5" width="9.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
     <col min="8" max="8" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.140625" style="1"/>
     <col min="10" max="10" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
+    <col min="11" max="11" width="0" style="1" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.140625" style="1"/>
     <col min="14" max="14" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -592,46 +596,30 @@
       <c r="A5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="17">
         <v>91.2</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15">
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17">
         <v>160</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15">
-        <v>240</v>
-      </c>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15">
-        <v>365</v>
-      </c>
-      <c r="U5" s="15"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="15"/>
-      <c r="Y5" s="15"/>
-      <c r="Z5" s="15">
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="Z5" s="17">
         <v>500</v>
       </c>
-      <c r="AA5" s="15"/>
-      <c r="AB5" s="15"/>
-      <c r="AC5" s="15"/>
-      <c r="AD5" s="15"/>
-      <c r="AE5" s="15"/>
+      <c r="AA5" s="17"/>
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="17"/>
+      <c r="AE5" s="17"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -650,7 +638,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>12</v>
@@ -668,45 +656,9 @@
         <v>13</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="R6" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="S6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="V6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="W6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="X6" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y6" s="9" t="s">
         <v>13</v>
       </c>
       <c r="Z6" s="3" t="s">
@@ -735,10 +687,7 @@
       <c r="B7" s="4">
         <v>430955</v>
       </c>
-      <c r="C7" s="5">
-        <f>B7*G7/F7</f>
-        <v>13.096722450000001</v>
-      </c>
+      <c r="C7" s="5"/>
       <c r="D7" s="7">
         <v>569045</v>
       </c>
@@ -756,10 +705,7 @@
       <c r="H7" s="4">
         <v>74115</v>
       </c>
-      <c r="I7" s="5">
-        <f>H7*M$7/L$7</f>
-        <v>11.295126</v>
-      </c>
+      <c r="I7" s="5"/>
       <c r="J7" s="7">
         <v>925885</v>
       </c>
@@ -774,48 +720,6 @@
       <c r="M7" s="11">
         <v>152.4</v>
       </c>
-      <c r="N7" s="4">
-        <v>97055</v>
-      </c>
-      <c r="O7" s="5">
-        <f>N7*S$7/R$7</f>
-        <v>5.8524165000000004</v>
-      </c>
-      <c r="P7" s="7">
-        <v>902945</v>
-      </c>
-      <c r="Q7" s="8">
-        <f>P7*S$7/R$7</f>
-        <v>54.4475835</v>
-      </c>
-      <c r="R7" s="10">
-        <f>N7+P7</f>
-        <v>1000000</v>
-      </c>
-      <c r="S7" s="11">
-        <v>60.3</v>
-      </c>
-      <c r="T7" s="4">
-        <v>102525</v>
-      </c>
-      <c r="U7" s="5">
-        <f>T7*Y$7/X$7</f>
-        <v>2.7538214999999999</v>
-      </c>
-      <c r="V7" s="7">
-        <v>897475</v>
-      </c>
-      <c r="W7" s="8">
-        <f>V7*Y$7/X$7</f>
-        <v>24.106178499999999</v>
-      </c>
-      <c r="X7" s="10">
-        <f>T7+V7</f>
-        <v>1000000</v>
-      </c>
-      <c r="Y7" s="11">
-        <v>26.86</v>
-      </c>
       <c r="Z7" s="4">
         <v>105018</v>
       </c>
@@ -845,19 +749,16 @@
       <c r="B8" s="4">
         <v>430955</v>
       </c>
-      <c r="C8" s="5">
-        <f t="shared" ref="C8" si="1">B8*G8/F8</f>
-        <v>13.096722450000001</v>
-      </c>
+      <c r="C8" s="5"/>
       <c r="D8" s="7">
         <v>569045</v>
       </c>
       <c r="E8" s="8">
-        <f t="shared" ref="E8" si="2">D8*G8/F8</f>
+        <f t="shared" ref="E8" si="1">D8*G8/F8</f>
         <v>17.293277549999999</v>
       </c>
       <c r="F8" s="10">
-        <f t="shared" ref="F8" si="3">B8+D8</f>
+        <f>B8+D8</f>
         <v>1000000</v>
       </c>
       <c r="G8" s="11">
@@ -867,81 +768,34 @@
       <c r="H8" s="4">
         <v>70832</v>
       </c>
-      <c r="I8" s="5">
-        <f t="shared" ref="I8:I11" si="4">H8*M$7/L$7</f>
-        <v>10.7947968</v>
-      </c>
+      <c r="I8" s="5"/>
       <c r="J8" s="7">
         <v>921081</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" ref="K8:K11" si="5">J8*M$7/L$7</f>
+        <f t="shared" ref="K8:K11" si="2">J8*M$7/L$7</f>
         <v>140.37274440000002</v>
       </c>
       <c r="L8" s="10">
-        <f t="shared" ref="L8:L11" si="6">H8+J8</f>
+        <f>H8+J8</f>
         <v>991913</v>
       </c>
       <c r="M8" s="11">
         <f>L8*M$7/L$7</f>
         <v>151.16754120000002</v>
       </c>
-      <c r="N8" s="4">
-        <v>57323</v>
-      </c>
-      <c r="O8" s="5">
-        <f t="shared" ref="O8:O11" si="7">N8*S$7/R$7</f>
-        <v>3.4565769</v>
-      </c>
-      <c r="P8" s="7">
-        <v>806303</v>
-      </c>
-      <c r="Q8" s="8">
-        <f t="shared" ref="Q8:Q11" si="8">P8*S$7/R$7</f>
-        <v>48.620070900000002</v>
-      </c>
-      <c r="R8" s="10">
-        <f t="shared" ref="R8:R11" si="9">N8+P8</f>
-        <v>863626</v>
-      </c>
-      <c r="S8" s="11">
-        <f>R8*S$7/R$7</f>
-        <v>52.076647799999996</v>
-      </c>
-      <c r="T8" s="4">
-        <v>46173</v>
-      </c>
-      <c r="U8" s="5">
-        <f t="shared" ref="U8:U11" si="10">T8*Y$7/X$7</f>
-        <v>1.2402067800000001</v>
-      </c>
-      <c r="V8" s="7">
-        <v>738467</v>
-      </c>
-      <c r="W8" s="8">
-        <f t="shared" ref="W8:W11" si="11">V8*Y$7/X$7</f>
-        <v>19.835223620000001</v>
-      </c>
-      <c r="X8" s="10">
-        <f t="shared" ref="X8:X11" si="12">T8+V8</f>
-        <v>784640</v>
-      </c>
-      <c r="Y8" s="11">
-        <f>X8*Y$7/X$7</f>
-        <v>21.075430399999998</v>
-      </c>
       <c r="Z8" s="4">
         <v>39617</v>
       </c>
       <c r="AA8" s="5">
-        <f t="shared" ref="AA8:AA11" si="13">Z8*AE$7/AD$7</f>
+        <f t="shared" ref="AA8:AA11" si="3">Z8*AE$7/AD$7</f>
         <v>0.60812094999999999</v>
       </c>
       <c r="AB8" s="7">
         <v>687761</v>
       </c>
       <c r="AC8" s="8">
-        <f t="shared" ref="AC8:AC11" si="14">AB8*AE$7/AD$7</f>
+        <f t="shared" ref="AC8:AC11" si="4">AB8*AE$7/AD$7</f>
         <v>10.557131349999999</v>
       </c>
       <c r="AD8" s="10">
@@ -957,19 +811,16 @@
       <c r="A9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
       <c r="H9" s="4">
         <v>2843</v>
       </c>
-      <c r="I9" s="5">
-        <f>H9*M$7/L$7</f>
-        <v>0.43327320000000002</v>
-      </c>
+      <c r="I9" s="5"/>
       <c r="J9" s="7">
         <v>3941</v>
       </c>
@@ -985,50 +836,6 @@
         <f>L9*M$7/L$7</f>
         <v>1.0338816000000002</v>
       </c>
-      <c r="N9" s="4">
-        <v>36170</v>
-      </c>
-      <c r="O9" s="5">
-        <f>N9*S$7/R$7</f>
-        <v>2.1810510000000001</v>
-      </c>
-      <c r="P9" s="7">
-        <v>88073</v>
-      </c>
-      <c r="Q9" s="8">
-        <f>P9*S$7/R$7</f>
-        <v>5.3108018999999995</v>
-      </c>
-      <c r="R9" s="10">
-        <f>N9+P9</f>
-        <v>124243</v>
-      </c>
-      <c r="S9" s="11">
-        <f>R9*S$7/R$7</f>
-        <v>7.4918528999999996</v>
-      </c>
-      <c r="T9" s="4">
-        <v>49739</v>
-      </c>
-      <c r="U9" s="5">
-        <f>T9*Y$7/X$7</f>
-        <v>1.3359895400000001</v>
-      </c>
-      <c r="V9" s="7">
-        <v>140943</v>
-      </c>
-      <c r="W9" s="8">
-        <f>V9*Y$7/X$7</f>
-        <v>3.78572898</v>
-      </c>
-      <c r="X9" s="10">
-        <f>T9+V9</f>
-        <v>190682</v>
-      </c>
-      <c r="Y9" s="11">
-        <f>X9*Y$7/X$7</f>
-        <v>5.1217185199999999</v>
-      </c>
       <c r="Z9" s="4">
         <v>56185</v>
       </c>
@@ -1056,90 +863,43 @@
       <c r="A10" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
       <c r="H10" s="4">
         <v>439</v>
       </c>
-      <c r="I10" s="5">
-        <f t="shared" si="4"/>
-        <v>6.6903600000000008E-2</v>
-      </c>
+      <c r="I10" s="5"/>
       <c r="J10" s="7">
         <v>862</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0.13136880000000001</v>
       </c>
       <c r="L10" s="10">
-        <f t="shared" si="6"/>
+        <f>H10+J10</f>
         <v>1301</v>
       </c>
       <c r="M10" s="11">
-        <f t="shared" ref="M10:M11" si="15">L10*M$7/L$7</f>
+        <f t="shared" ref="M10:M11" si="5">L10*M$7/L$7</f>
         <v>0.19827239999999999</v>
-      </c>
-      <c r="N10" s="4">
-        <v>3134</v>
-      </c>
-      <c r="O10" s="5">
-        <f t="shared" si="7"/>
-        <v>0.18898019999999999</v>
-      </c>
-      <c r="P10" s="7">
-        <v>7531</v>
-      </c>
-      <c r="Q10" s="8">
-        <f t="shared" si="8"/>
-        <v>0.4541193</v>
-      </c>
-      <c r="R10" s="10">
-        <f t="shared" si="9"/>
-        <v>10665</v>
-      </c>
-      <c r="S10" s="11">
-        <f t="shared" ref="S10:S11" si="16">R10*S$7/R$7</f>
-        <v>0.64309950000000005</v>
-      </c>
-      <c r="T10" s="4">
-        <v>3892</v>
-      </c>
-      <c r="U10" s="5">
-        <f t="shared" si="10"/>
-        <v>0.10453912</v>
-      </c>
-      <c r="V10" s="7">
-        <v>11138</v>
-      </c>
-      <c r="W10" s="8">
-        <f t="shared" si="11"/>
-        <v>0.29916668000000002</v>
-      </c>
-      <c r="X10" s="10">
-        <f t="shared" si="12"/>
-        <v>15030</v>
-      </c>
-      <c r="Y10" s="11">
-        <f t="shared" ref="Y10:Y11" si="17">X10*Y$7/X$7</f>
-        <v>0.4037058</v>
       </c>
       <c r="Z10" s="4">
         <v>4226</v>
       </c>
       <c r="AA10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>6.4869099999999999E-2</v>
       </c>
       <c r="AB10" s="7">
         <v>13361</v>
       </c>
       <c r="AC10" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="4"/>
         <v>0.20509135000000001</v>
       </c>
       <c r="AD10" s="10">
@@ -1147,7 +907,7 @@
         <v>17587</v>
       </c>
       <c r="AE10" s="12">
-        <f t="shared" ref="AE10:AE11" si="18">AD10*AE$7/AD$7</f>
+        <f t="shared" ref="AE10:AE11" si="6">AD10*AE$7/AD$7</f>
         <v>0.26996045000000002</v>
       </c>
     </row>
@@ -1155,90 +915,43 @@
       <c r="A11" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="17"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
       <c r="H11" s="4">
         <v>1</v>
       </c>
-      <c r="I11" s="5">
-        <f t="shared" si="4"/>
-        <v>1.5240000000000002E-4</v>
-      </c>
+      <c r="I11" s="5"/>
       <c r="J11" s="7">
         <v>1</v>
       </c>
       <c r="K11" s="8">
+        <f t="shared" si="2"/>
+        <v>1.5240000000000002E-4</v>
+      </c>
+      <c r="L11" s="10">
+        <f>H11+J11</f>
+        <v>2</v>
+      </c>
+      <c r="M11" s="11">
         <f t="shared" si="5"/>
-        <v>1.5240000000000002E-4</v>
-      </c>
-      <c r="L11" s="10">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="M11" s="11">
-        <f t="shared" si="15"/>
         <v>3.0480000000000004E-4</v>
-      </c>
-      <c r="N11" s="4">
-        <v>15</v>
-      </c>
-      <c r="O11" s="5">
-        <f t="shared" si="7"/>
-        <v>9.0450000000000003E-4</v>
-      </c>
-      <c r="P11" s="7">
-        <v>44</v>
-      </c>
-      <c r="Q11" s="8">
-        <f t="shared" si="8"/>
-        <v>2.6531999999999997E-3</v>
-      </c>
-      <c r="R11" s="10">
-        <f t="shared" si="9"/>
-        <v>59</v>
-      </c>
-      <c r="S11" s="11">
-        <f t="shared" si="16"/>
-        <v>3.5577E-3</v>
-      </c>
-      <c r="T11" s="4">
-        <v>208</v>
-      </c>
-      <c r="U11" s="5">
-        <f t="shared" si="10"/>
-        <v>5.5868799999999998E-3</v>
-      </c>
-      <c r="V11" s="7">
-        <v>517</v>
-      </c>
-      <c r="W11" s="8">
-        <f t="shared" si="11"/>
-        <v>1.3886619999999999E-2</v>
-      </c>
-      <c r="X11" s="10">
-        <f t="shared" si="12"/>
-        <v>725</v>
-      </c>
-      <c r="Y11" s="11">
-        <f t="shared" si="17"/>
-        <v>1.9473500000000001E-2</v>
       </c>
       <c r="Z11" s="4">
         <v>752</v>
       </c>
       <c r="AA11" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>1.1543199999999998E-2</v>
       </c>
       <c r="AB11" s="7">
         <v>2005</v>
       </c>
       <c r="AC11" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="4"/>
         <v>3.0776749999999999E-2</v>
       </c>
       <c r="AD11" s="10">
@@ -1246,7 +959,7 @@
         <v>2757</v>
       </c>
       <c r="AE11" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="6"/>
         <v>4.2319949999999995E-2</v>
       </c>
     </row>
@@ -1254,62 +967,18 @@
       <c r="A12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="4">
-        <v>413</v>
-      </c>
-      <c r="O12" s="5">
-        <f>N12*S$7/R$7</f>
-        <v>2.4903899999999996E-2</v>
-      </c>
-      <c r="P12" s="7">
-        <v>994</v>
-      </c>
-      <c r="Q12" s="8">
-        <f>P12*S$7/R$7</f>
-        <v>5.9938199999999997E-2</v>
-      </c>
-      <c r="R12" s="10">
-        <f>N12+P12</f>
-        <v>1407</v>
-      </c>
-      <c r="S12" s="11">
-        <f>R12*S$7/R$7</f>
-        <v>8.484209999999999E-2</v>
-      </c>
-      <c r="T12" s="4">
-        <v>508</v>
-      </c>
-      <c r="U12" s="5">
-        <f>T12*Y$7/X$7</f>
-        <v>1.364488E-2</v>
-      </c>
-      <c r="V12" s="7">
-        <v>1601</v>
-      </c>
-      <c r="W12" s="8">
-        <f>V12*Y$7/X$7</f>
-        <v>4.3002860000000004E-2</v>
-      </c>
-      <c r="X12" s="10">
-        <f>T12+V12</f>
-        <v>2109</v>
-      </c>
-      <c r="Y12" s="11">
-        <f>X12*Y$7/X$7</f>
-        <v>5.6647739999999995E-2</v>
-      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="16"/>
       <c r="Z12" s="4">
         <v>395</v>
       </c>
@@ -1337,46 +1006,18 @@
       <c r="A13" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="4">
-        <v>2005</v>
-      </c>
-      <c r="U13" s="5">
-        <f>T13*Y$7/X$7</f>
-        <v>5.3854299999999994E-2</v>
-      </c>
-      <c r="V13" s="7">
-        <v>4809</v>
-      </c>
-      <c r="W13" s="8">
-        <f>V13*Y$7/X$7</f>
-        <v>0.12916973999999998</v>
-      </c>
-      <c r="X13" s="10">
-        <f>T13+V13</f>
-        <v>6814</v>
-      </c>
-      <c r="Y13" s="11">
-        <f>X13*Y$7/X$7</f>
-        <v>0.18302404</v>
-      </c>
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="16"/>
       <c r="Z13" s="4">
         <v>3843</v>
       </c>
@@ -1401,14 +1042,360 @@
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="17">
+        <v>240</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17">
+        <v>365</v>
+      </c>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
       <c r="Y14" s="2"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="4">
+        <v>97055</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="7">
+        <v>902945</v>
+      </c>
+      <c r="E16" s="8">
+        <f>D16*G$16/F$16</f>
+        <v>54.4475835</v>
+      </c>
+      <c r="F16" s="10">
+        <f>B16+D16</f>
+        <v>1000000</v>
+      </c>
+      <c r="G16" s="11">
+        <v>60.3</v>
+      </c>
+      <c r="H16" s="4">
+        <v>102525</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="7">
+        <v>897475</v>
+      </c>
+      <c r="K16" s="8">
+        <f>J16*M$16/L$16</f>
+        <v>24.106178499999999</v>
+      </c>
+      <c r="L16" s="10">
+        <f>H16+J16</f>
+        <v>1000000</v>
+      </c>
+      <c r="M16" s="11">
+        <v>26.86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4">
+        <v>57323</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="7">
+        <v>806303</v>
+      </c>
+      <c r="E17" s="8">
+        <f>D17*G$16/F$16</f>
+        <v>48.620070900000002</v>
+      </c>
+      <c r="F17" s="10">
+        <f>B17+D17</f>
+        <v>863626</v>
+      </c>
+      <c r="G17" s="11">
+        <f>F17*G$16/F$16</f>
+        <v>52.076647799999996</v>
+      </c>
+      <c r="H17" s="4">
+        <v>46173</v>
+      </c>
+      <c r="I17" s="5"/>
+      <c r="J17" s="7">
+        <v>738467</v>
+      </c>
+      <c r="K17" s="8">
+        <f>J17*M$16/L$16</f>
+        <v>19.835223620000001</v>
+      </c>
+      <c r="L17" s="10">
+        <f>H17+J17</f>
+        <v>784640</v>
+      </c>
+      <c r="M17" s="11">
+        <f>L17*M$16/L$16</f>
+        <v>21.075430399999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="4">
+        <v>36170</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="7">
+        <v>88073</v>
+      </c>
+      <c r="E18" s="8">
+        <f>D18*G$16/F$16</f>
+        <v>5.3108018999999995</v>
+      </c>
+      <c r="F18" s="10">
+        <f>B18+D18</f>
+        <v>124243</v>
+      </c>
+      <c r="G18" s="11">
+        <f>F18*G$16/F$16</f>
+        <v>7.4918528999999996</v>
+      </c>
+      <c r="H18" s="4">
+        <v>49739</v>
+      </c>
+      <c r="I18" s="5"/>
+      <c r="J18" s="7">
+        <v>140943</v>
+      </c>
+      <c r="K18" s="8">
+        <f>J18*M$16/L$16</f>
+        <v>3.78572898</v>
+      </c>
+      <c r="L18" s="10">
+        <f>H18+J18</f>
+        <v>190682</v>
+      </c>
+      <c r="M18" s="11">
+        <f>L18*M$16/L$16</f>
+        <v>5.1217185199999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="4">
+        <v>3134</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="7">
+        <v>7531</v>
+      </c>
+      <c r="E19" s="8">
+        <f>D19*G$16/F$16</f>
+        <v>0.4541193</v>
+      </c>
+      <c r="F19" s="10">
+        <f>B19+D19</f>
+        <v>10665</v>
+      </c>
+      <c r="G19" s="11">
+        <f>F19*G$16/F$16</f>
+        <v>0.64309950000000005</v>
+      </c>
+      <c r="H19" s="4">
+        <v>3892</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="7">
+        <v>11138</v>
+      </c>
+      <c r="K19" s="8">
+        <f>J19*M$16/L$16</f>
+        <v>0.29916668000000002</v>
+      </c>
+      <c r="L19" s="10">
+        <f>H19+J19</f>
+        <v>15030</v>
+      </c>
+      <c r="M19" s="11">
+        <f>L19*M$16/L$16</f>
+        <v>0.4037058</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="4">
+        <v>15</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="7">
+        <v>44</v>
+      </c>
+      <c r="E20" s="8">
+        <f>D20*G$16/F$16</f>
+        <v>2.6531999999999997E-3</v>
+      </c>
+      <c r="F20" s="10">
+        <f>B20+D20</f>
+        <v>59</v>
+      </c>
+      <c r="G20" s="11">
+        <f>F20*G$16/F$16</f>
+        <v>3.5577E-3</v>
+      </c>
+      <c r="H20" s="4">
+        <v>208</v>
+      </c>
+      <c r="I20" s="5"/>
+      <c r="J20" s="7">
+        <v>517</v>
+      </c>
+      <c r="K20" s="8">
+        <f>J20*M$16/L$16</f>
+        <v>1.3886619999999999E-2</v>
+      </c>
+      <c r="L20" s="10">
+        <f>H20+J20</f>
+        <v>725</v>
+      </c>
+      <c r="M20" s="11">
+        <f>L20*M$16/L$16</f>
+        <v>1.9473500000000001E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="4">
+        <v>413</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="7">
+        <v>994</v>
+      </c>
+      <c r="E21" s="8">
+        <f>D21*G$16/F$16</f>
+        <v>5.9938199999999997E-2</v>
+      </c>
+      <c r="F21" s="10">
+        <f>B21+D21</f>
+        <v>1407</v>
+      </c>
+      <c r="G21" s="11">
+        <f>F21*G$16/F$16</f>
+        <v>8.484209999999999E-2</v>
+      </c>
+      <c r="H21" s="4">
+        <v>508</v>
+      </c>
+      <c r="I21" s="5"/>
+      <c r="J21" s="7">
+        <v>1601</v>
+      </c>
+      <c r="K21" s="8">
+        <f>J21*M$16/L$16</f>
+        <v>4.3002860000000004E-2</v>
+      </c>
+      <c r="L21" s="10">
+        <f>H21+J21</f>
+        <v>2109</v>
+      </c>
+      <c r="M21" s="11">
+        <f>L21*M$16/L$16</f>
+        <v>5.6647739999999995E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="15"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="4">
+        <v>2005</v>
+      </c>
+      <c r="I22" s="5"/>
+      <c r="J22" s="7">
+        <v>4809</v>
+      </c>
+      <c r="K22" s="8">
+        <f>J22*M$16/L$16</f>
+        <v>0.12916973999999998</v>
+      </c>
+      <c r="L22" s="10">
+        <f>H22+J22</f>
+        <v>6814</v>
+      </c>
+      <c r="M22" s="11">
+        <f>L22*M$16/L$16</f>
+        <v>0.18302404</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="H5:M5"/>
-    <mergeCell ref="N5:S5"/>
-    <mergeCell ref="T5:Y5"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="H14:M14"/>
     <mergeCell ref="Z5:AE5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/7-TESLA_500G_Calibration/barns.xlsx
+++ b/7-TESLA_500G_Calibration/barns.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmathew\cernbox\WINDOWS\Desktop\Git-Projects\HEP-Pheno-Project\7-TESLA_500G_Calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC750869-B72E-4DC5-97C2-1452CAA80AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA80CC1-957A-4546-9205-C67322479FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{7960ABCD-F717-4580-A97E-BFEE89018374}"/>
   </bookViews>
@@ -174,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -223,6 +223,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -238,6 +239,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>65484</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>75320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>603853</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>167470</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC48684B-FB7B-C018-2609-B9E83C36363B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="65484" y="4266320"/>
+          <a:ext cx="7003463" cy="1997150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -784,6 +834,9 @@
         <f>L8*M$7/L$7</f>
         <v>151.16754120000002</v>
       </c>
+      <c r="O8" s="18">
+        <v>5000000</v>
+      </c>
       <c r="Z8" s="4">
         <v>39617</v>
       </c>
@@ -887,6 +940,10 @@
       <c r="M10" s="11">
         <f t="shared" ref="M10:M11" si="5">L10*M$7/L$7</f>
         <v>0.19827239999999999</v>
+      </c>
+      <c r="O10" s="18">
+        <f>G7*O8</f>
+        <v>151950000</v>
       </c>
       <c r="Z10" s="4">
         <v>4226</v>
@@ -1116,11 +1173,11 @@
         <v>902945</v>
       </c>
       <c r="E16" s="8">
-        <f>D16*G$16/F$16</f>
+        <f t="shared" ref="E16:E21" si="7">D16*G$16/F$16</f>
         <v>54.4475835</v>
       </c>
       <c r="F16" s="10">
-        <f>B16+D16</f>
+        <f t="shared" ref="F16:F21" si="8">B16+D16</f>
         <v>1000000</v>
       </c>
       <c r="G16" s="11">
@@ -1134,11 +1191,11 @@
         <v>897475</v>
       </c>
       <c r="K16" s="8">
-        <f>J16*M$16/L$16</f>
+        <f t="shared" ref="K16:K22" si="9">J16*M$16/L$16</f>
         <v>24.106178499999999</v>
       </c>
       <c r="L16" s="10">
-        <f>H16+J16</f>
+        <f t="shared" ref="L16:L22" si="10">H16+J16</f>
         <v>1000000</v>
       </c>
       <c r="M16" s="11">
@@ -1157,11 +1214,11 @@
         <v>806303</v>
       </c>
       <c r="E17" s="8">
-        <f>D17*G$16/F$16</f>
+        <f t="shared" si="7"/>
         <v>48.620070900000002</v>
       </c>
       <c r="F17" s="10">
-        <f>B17+D17</f>
+        <f t="shared" si="8"/>
         <v>863626</v>
       </c>
       <c r="G17" s="11">
@@ -1176,15 +1233,15 @@
         <v>738467</v>
       </c>
       <c r="K17" s="8">
-        <f>J17*M$16/L$16</f>
+        <f t="shared" si="9"/>
         <v>19.835223620000001</v>
       </c>
       <c r="L17" s="10">
-        <f>H17+J17</f>
+        <f t="shared" si="10"/>
         <v>784640</v>
       </c>
       <c r="M17" s="11">
-        <f>L17*M$16/L$16</f>
+        <f t="shared" ref="M17:M22" si="11">L17*M$16/L$16</f>
         <v>21.075430399999998</v>
       </c>
     </row>
@@ -1200,11 +1257,11 @@
         <v>88073</v>
       </c>
       <c r="E18" s="8">
-        <f>D18*G$16/F$16</f>
+        <f t="shared" si="7"/>
         <v>5.3108018999999995</v>
       </c>
       <c r="F18" s="10">
-        <f>B18+D18</f>
+        <f t="shared" si="8"/>
         <v>124243</v>
       </c>
       <c r="G18" s="11">
@@ -1219,15 +1276,15 @@
         <v>140943</v>
       </c>
       <c r="K18" s="8">
-        <f>J18*M$16/L$16</f>
+        <f t="shared" si="9"/>
         <v>3.78572898</v>
       </c>
       <c r="L18" s="10">
-        <f>H18+J18</f>
+        <f t="shared" si="10"/>
         <v>190682</v>
       </c>
       <c r="M18" s="11">
-        <f>L18*M$16/L$16</f>
+        <f t="shared" si="11"/>
         <v>5.1217185199999999</v>
       </c>
     </row>
@@ -1243,11 +1300,11 @@
         <v>7531</v>
       </c>
       <c r="E19" s="8">
-        <f>D19*G$16/F$16</f>
+        <f t="shared" si="7"/>
         <v>0.4541193</v>
       </c>
       <c r="F19" s="10">
-        <f>B19+D19</f>
+        <f t="shared" si="8"/>
         <v>10665</v>
       </c>
       <c r="G19" s="11">
@@ -1262,15 +1319,15 @@
         <v>11138</v>
       </c>
       <c r="K19" s="8">
-        <f>J19*M$16/L$16</f>
+        <f t="shared" si="9"/>
         <v>0.29916668000000002</v>
       </c>
       <c r="L19" s="10">
-        <f>H19+J19</f>
+        <f t="shared" si="10"/>
         <v>15030</v>
       </c>
       <c r="M19" s="11">
-        <f>L19*M$16/L$16</f>
+        <f t="shared" si="11"/>
         <v>0.4037058</v>
       </c>
     </row>
@@ -1286,11 +1343,11 @@
         <v>44</v>
       </c>
       <c r="E20" s="8">
-        <f>D20*G$16/F$16</f>
+        <f t="shared" si="7"/>
         <v>2.6531999999999997E-3</v>
       </c>
       <c r="F20" s="10">
-        <f>B20+D20</f>
+        <f t="shared" si="8"/>
         <v>59</v>
       </c>
       <c r="G20" s="11">
@@ -1305,15 +1362,15 @@
         <v>517</v>
       </c>
       <c r="K20" s="8">
-        <f>J20*M$16/L$16</f>
+        <f t="shared" si="9"/>
         <v>1.3886619999999999E-2</v>
       </c>
       <c r="L20" s="10">
-        <f>H20+J20</f>
+        <f t="shared" si="10"/>
         <v>725</v>
       </c>
       <c r="M20" s="11">
-        <f>L20*M$16/L$16</f>
+        <f t="shared" si="11"/>
         <v>1.9473500000000001E-2</v>
       </c>
     </row>
@@ -1329,11 +1386,11 @@
         <v>994</v>
       </c>
       <c r="E21" s="8">
-        <f>D21*G$16/F$16</f>
+        <f t="shared" si="7"/>
         <v>5.9938199999999997E-2</v>
       </c>
       <c r="F21" s="10">
-        <f>B21+D21</f>
+        <f t="shared" si="8"/>
         <v>1407</v>
       </c>
       <c r="G21" s="11">
@@ -1348,15 +1405,15 @@
         <v>1601</v>
       </c>
       <c r="K21" s="8">
-        <f>J21*M$16/L$16</f>
+        <f t="shared" si="9"/>
         <v>4.3002860000000004E-2</v>
       </c>
       <c r="L21" s="10">
-        <f>H21+J21</f>
+        <f t="shared" si="10"/>
         <v>2109</v>
       </c>
       <c r="M21" s="11">
-        <f>L21*M$16/L$16</f>
+        <f t="shared" si="11"/>
         <v>5.6647739999999995E-2</v>
       </c>
     </row>
@@ -1378,15 +1435,15 @@
         <v>4809</v>
       </c>
       <c r="K22" s="8">
-        <f>J22*M$16/L$16</f>
+        <f t="shared" si="9"/>
         <v>0.12916973999999998</v>
       </c>
       <c r="L22" s="10">
-        <f>H22+J22</f>
+        <f t="shared" si="10"/>
         <v>6814</v>
       </c>
       <c r="M22" s="11">
-        <f>L22*M$16/L$16</f>
+        <f t="shared" si="11"/>
         <v>0.18302404</v>
       </c>
     </row>
@@ -1400,5 +1457,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/7-TESLA_500G_Calibration/barns.xlsx
+++ b/7-TESLA_500G_Calibration/barns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmathew\cernbox\WINDOWS\Desktop\Git-Projects\HEP-Pheno-Project\7-TESLA_500G_Calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA80CC1-957A-4546-9205-C67322479FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB4571A-8F22-4B46-9FD0-B9E995C2FAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{7960ABCD-F717-4580-A97E-BFEE89018374}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{7960ABCD-F717-4580-A97E-BFEE89018374}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -220,10 +220,10 @@
     <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -646,30 +646,30 @@
       <c r="A5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="18">
         <v>91.2</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17">
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18">
         <v>160</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="Z5" s="17">
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="Z5" s="18">
         <v>500</v>
       </c>
-      <c r="AA5" s="17"/>
-      <c r="AB5" s="17"/>
-      <c r="AC5" s="17"/>
-      <c r="AD5" s="17"/>
-      <c r="AE5" s="17"/>
+      <c r="AA5" s="18"/>
+      <c r="AB5" s="18"/>
+      <c r="AC5" s="18"/>
+      <c r="AD5" s="18"/>
+      <c r="AE5" s="18"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -834,9 +834,7 @@
         <f>L8*M$7/L$7</f>
         <v>151.16754120000002</v>
       </c>
-      <c r="O8" s="18">
-        <v>5000000</v>
-      </c>
+      <c r="O8" s="17"/>
       <c r="Z8" s="4">
         <v>39617</v>
       </c>
@@ -941,10 +939,7 @@
         <f t="shared" ref="M10:M11" si="5">L10*M$7/L$7</f>
         <v>0.19827239999999999</v>
       </c>
-      <c r="O10" s="18">
-        <f>G7*O8</f>
-        <v>151950000</v>
-      </c>
+      <c r="O10" s="17"/>
       <c r="Z10" s="4">
         <v>4226</v>
       </c>
@@ -1102,22 +1097,22 @@
       <c r="A14" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="18">
         <v>240</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17">
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18">
         <v>365</v>
       </c>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
       <c r="Y14" s="2"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">

--- a/7-TESLA_500G_Calibration/barns.xlsx
+++ b/7-TESLA_500G_Calibration/barns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmathew\cernbox\WINDOWS\Desktop\Git-Projects\HEP-Pheno-Project\7-TESLA_500G_Calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB4571A-8F22-4B46-9FD0-B9E995C2FAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FEE44B-9596-4261-A203-D5B48D8FB745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{7960ABCD-F717-4580-A97E-BFEE89018374}"/>
   </bookViews>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8C8F55F-93F0-4A61-B4C8-B8A5CBE0D442}">
-  <dimension ref="A5:AE22"/>
+  <dimension ref="A5:AE27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1155,6 +1155,18 @@
       <c r="M15" s="9" t="s">
         <v>13</v>
       </c>
+      <c r="O15" s="2">
+        <f>D7/F7</f>
+        <v>0.56904500000000002</v>
+      </c>
+      <c r="P15" s="2">
+        <f>J7/L7</f>
+        <v>0.92588499999999996</v>
+      </c>
+      <c r="Q15" s="1" t="str">
+        <f>A7</f>
+        <v>al</v>
+      </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
@@ -1196,8 +1208,20 @@
       <c r="M16" s="11">
         <v>26.86</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O16" s="2">
+        <f>D8/F8</f>
+        <v>0.56904500000000002</v>
+      </c>
+      <c r="P16" s="2">
+        <f>J8/L8</f>
+        <v>0.9285905114662274</v>
+      </c>
+      <c r="Q16" s="1" t="str">
+        <f t="shared" ref="Q16:Q19" si="11">A8</f>
+        <v>gZ</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>1</v>
       </c>
@@ -1236,11 +1260,19 @@
         <v>784640</v>
       </c>
       <c r="M17" s="11">
-        <f t="shared" ref="M17:M22" si="11">L17*M$16/L$16</f>
+        <f t="shared" ref="M17:M22" si="12">L17*M$16/L$16</f>
         <v>21.075430399999998</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="P17" s="2">
+        <f t="shared" ref="P17:P20" si="13">J9/L9</f>
+        <v>0.58092570754716977</v>
+      </c>
+      <c r="Q17" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>WW</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>3</v>
       </c>
@@ -1279,11 +1311,19 @@
         <v>190682</v>
       </c>
       <c r="M18" s="11">
+        <f t="shared" si="12"/>
+        <v>5.1217185199999999</v>
+      </c>
+      <c r="P18" s="2">
+        <f t="shared" si="13"/>
+        <v>0.6625672559569562</v>
+      </c>
+      <c r="Q18" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>5.1217185199999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>ZZ</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>2</v>
       </c>
@@ -1322,11 +1362,19 @@
         <v>15030</v>
       </c>
       <c r="M19" s="11">
+        <f t="shared" si="12"/>
+        <v>0.4037058</v>
+      </c>
+      <c r="P19" s="2">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>0.4037058</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>HW</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>6</v>
       </c>
@@ -1365,11 +1413,23 @@
         <v>725</v>
       </c>
       <c r="M20" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.9473500000000001E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O20" s="2">
+        <f>D16/F16</f>
+        <v>0.902945</v>
+      </c>
+      <c r="P20" s="2">
+        <f>J16/L16</f>
+        <v>0.89747500000000002</v>
+      </c>
+      <c r="Q20" s="1" t="str">
+        <f>A16</f>
+        <v>al</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>5</v>
       </c>
@@ -1408,11 +1468,23 @@
         <v>2109</v>
       </c>
       <c r="M21" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.6647739999999995E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O21" s="2">
+        <f>D17/F17</f>
+        <v>0.93362520350244205</v>
+      </c>
+      <c r="P21" s="2">
+        <f>J17/L17</f>
+        <v>0.9411539049755302</v>
+      </c>
+      <c r="Q21" s="1" t="str">
+        <f t="shared" ref="Q21:Q26" si="14">A17</f>
+        <v>gZ</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>4</v>
       </c>
@@ -1438,9 +1510,78 @@
         <v>6814</v>
       </c>
       <c r="M22" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.18302404</v>
       </c>
+      <c r="O22" s="2">
+        <f t="shared" ref="O22:O27" si="15">D18/F18</f>
+        <v>0.70887695886287361</v>
+      </c>
+      <c r="P22" s="2">
+        <f t="shared" ref="P22:P25" si="16">J18/L18</f>
+        <v>0.73915209616009903</v>
+      </c>
+      <c r="Q22" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>WW</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O23" s="2">
+        <f t="shared" si="15"/>
+        <v>0.70614158462259724</v>
+      </c>
+      <c r="P23" s="2">
+        <f t="shared" si="16"/>
+        <v>0.74105123087159019</v>
+      </c>
+      <c r="Q23" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>ZZ</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O24" s="2">
+        <f t="shared" si="15"/>
+        <v>0.74576271186440679</v>
+      </c>
+      <c r="P24" s="2">
+        <f t="shared" si="16"/>
+        <v>0.71310344827586203</v>
+      </c>
+      <c r="Q24" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>HW</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O25" s="2">
+        <f t="shared" si="15"/>
+        <v>0.70646766169154229</v>
+      </c>
+      <c r="P25" s="2">
+        <f t="shared" si="16"/>
+        <v>0.75912754860123277</v>
+      </c>
+      <c r="Q25" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>HZ</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O26" s="2"/>
+      <c r="P26" s="2">
+        <f>J22/L22</f>
+        <v>0.7057528617552099</v>
+      </c>
+      <c r="Q26" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>tt</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/7-TESLA_500G_Calibration/barns.xlsx
+++ b/7-TESLA_500G_Calibration/barns.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmathew\cernbox\WINDOWS\Desktop\Git-Projects\HEP-Pheno-Project\7-TESLA_500G_Calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FEE44B-9596-4261-A203-D5B48D8FB745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08712ACB-D1D8-4810-96E3-FFA63521C0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{7960ABCD-F717-4580-A97E-BFEE89018374}"/>
+    <workbookView xWindow="10785" yWindow="3570" windowWidth="12360" windowHeight="15375" activeTab="1" xr2:uid="{7960ABCD-F717-4580-A97E-BFEE89018374}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ISR_ON_1M" sheetId="3" r:id="rId1"/>
+    <sheet name="ISR_ON_5M" sheetId="1" r:id="rId2"/>
+    <sheet name="ISR_OF" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="15">
   <si>
     <t>al</t>
   </si>
@@ -87,6 +89,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -174,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -224,6 +229,17 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -261,7 +277,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC48684B-FB7B-C018-2609-B9E83C36363B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77C58325-EFA4-45E2-8B62-739018E723D1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -278,7 +294,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="65484" y="4266320"/>
-          <a:ext cx="7003463" cy="1997150"/>
+          <a:ext cx="7024894" cy="1997150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -606,8 +622,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8C8F55F-93F0-4A61-B4C8-B8A5CBE0D442}">
-  <dimension ref="A5:AE27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B181031-C592-4223-BD1B-7DB014710974}">
+  <dimension ref="A5:AE45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -646,30 +662,30 @@
       <c r="A5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="23">
         <v>91.2</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18">
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23">
         <v>160</v>
       </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18"/>
-      <c r="Z5" s="18">
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="Z5" s="23">
         <v>500</v>
       </c>
-      <c r="AA5" s="18"/>
-      <c r="AB5" s="18"/>
-      <c r="AC5" s="18"/>
-      <c r="AD5" s="18"/>
-      <c r="AE5" s="18"/>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="23"/>
+      <c r="AC5" s="23"/>
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="23"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -1097,22 +1113,22 @@
       <c r="A14" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="23">
         <v>240</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18">
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23">
         <v>365</v>
       </c>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
       <c r="Y14" s="2"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
@@ -1264,7 +1280,7 @@
         <v>21.075430399999998</v>
       </c>
       <c r="P17" s="2">
-        <f t="shared" ref="P17:P20" si="13">J9/L9</f>
+        <f t="shared" ref="P17:P19" si="13">J9/L9</f>
         <v>0.58092570754716977</v>
       </c>
       <c r="Q17" s="1" t="str">
@@ -1514,7 +1530,7 @@
         <v>0.18302404</v>
       </c>
       <c r="O22" s="2">
-        <f t="shared" ref="O22:O27" si="15">D18/F18</f>
+        <f t="shared" ref="O22:O25" si="15">D18/F18</f>
         <v>0.70887695886287361</v>
       </c>
       <c r="P22" s="2">
@@ -1582,6 +1598,1066 @@
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
+    </row>
+    <row r="35" spans="13:20" x14ac:dyDescent="0.25">
+      <c r="P35" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>160</v>
+      </c>
+      <c r="R35" s="1">
+        <v>240</v>
+      </c>
+      <c r="S35" s="1">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="36" spans="13:20" x14ac:dyDescent="0.25">
+      <c r="O36" s="1">
+        <v>100</v>
+      </c>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="19"/>
+      <c r="S36" s="19"/>
+      <c r="T36" s="17"/>
+    </row>
+    <row r="37" spans="13:20" x14ac:dyDescent="0.25">
+      <c r="O37" s="1">
+        <v>95</v>
+      </c>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="19"/>
+      <c r="S37" s="19"/>
+      <c r="T37" s="17"/>
+    </row>
+    <row r="38" spans="13:20" x14ac:dyDescent="0.25">
+      <c r="O38" s="1">
+        <v>90</v>
+      </c>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="19"/>
+      <c r="R38" s="19"/>
+      <c r="S38" s="19"/>
+      <c r="T38" s="17"/>
+    </row>
+    <row r="39" spans="13:20" x14ac:dyDescent="0.25">
+      <c r="O39" s="1">
+        <v>85</v>
+      </c>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="19"/>
+      <c r="R39" s="19"/>
+      <c r="S39" s="19"/>
+      <c r="T39" s="17"/>
+    </row>
+    <row r="45" spans="13:20" x14ac:dyDescent="0.25">
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="Z5:AE5"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="H14:M14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8C8F55F-93F0-4A61-B4C8-B8A5CBE0D442}">
+  <dimension ref="A5:AE45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="4" max="4" width="9.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="8" max="8" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="1"/>
+    <col min="14" max="14" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="1"/>
+    <col min="18" max="18" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" style="1"/>
+    <col min="20" max="20" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" style="1"/>
+    <col min="22" max="22" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.140625" style="1"/>
+    <col min="24" max="25" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.140625" style="1"/>
+    <col min="28" max="28" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.140625" style="1"/>
+    <col min="30" max="31" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="23">
+        <v>91.2</v>
+      </c>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23">
+        <v>160</v>
+      </c>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="Z5" s="23">
+        <v>500</v>
+      </c>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="23"/>
+      <c r="AC5" s="23"/>
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="23"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE6" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8" t="e">
+        <f>D7*G7/F7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F7" s="10">
+        <f>B7+D7</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="11">
+        <v>30.39</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="8" t="e">
+        <f>J7*M$7/L$7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L7" s="10">
+        <f>H7+J7</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="11">
+        <v>152.4</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>105018</v>
+      </c>
+      <c r="AA7" s="5">
+        <f>Z7*AE$7/AD$7</f>
+        <v>1.6120263000000001</v>
+      </c>
+      <c r="AB7" s="7">
+        <v>894982</v>
+      </c>
+      <c r="AC7" s="8">
+        <f>AB7*AE$7/AD$7</f>
+        <v>13.7379737</v>
+      </c>
+      <c r="AD7" s="10">
+        <f t="shared" ref="AD7:AD13" si="0">Z7+AB7</f>
+        <v>1000000</v>
+      </c>
+      <c r="AE7" s="11">
+        <v>15.35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8" t="e">
+        <f t="shared" ref="E8" si="1">D8*G8/F8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F8" s="10">
+        <f>B8+D8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="11" t="e">
+        <f>F8*G7/F7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="8" t="e">
+        <f t="shared" ref="K8:K11" si="2">J8*M$7/L$7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L8" s="10">
+        <f>H8+J8</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="11" t="e">
+        <f>L8*M$7/L$7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O8" s="17"/>
+      <c r="Z8" s="4">
+        <v>39617</v>
+      </c>
+      <c r="AA8" s="5">
+        <f t="shared" ref="AA8:AA11" si="3">Z8*AE$7/AD$7</f>
+        <v>0.60812094999999999</v>
+      </c>
+      <c r="AB8" s="7">
+        <v>687761</v>
+      </c>
+      <c r="AC8" s="8">
+        <f t="shared" ref="AC8:AC11" si="4">AB8*AE$7/AD$7</f>
+        <v>10.557131349999999</v>
+      </c>
+      <c r="AD8" s="10">
+        <f t="shared" si="0"/>
+        <v>727378</v>
+      </c>
+      <c r="AE8" s="12">
+        <f>AD8*AE$7/AD$7</f>
+        <v>11.165252299999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="8" t="e">
+        <f>J9*M$7/L$7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L9" s="10">
+        <f>H9+J9</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="11" t="e">
+        <f>L9*M$7/L$7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>56185</v>
+      </c>
+      <c r="AA9" s="5">
+        <f>Z9*AE$7/AD$7</f>
+        <v>0.86243974999999995</v>
+      </c>
+      <c r="AB9" s="7">
+        <v>176832</v>
+      </c>
+      <c r="AC9" s="8">
+        <f>AB9*AE$7/AD$7</f>
+        <v>2.7143711999999995</v>
+      </c>
+      <c r="AD9" s="10">
+        <f t="shared" si="0"/>
+        <v>233017</v>
+      </c>
+      <c r="AE9" s="12">
+        <f>AD9*AE$7/AD$7</f>
+        <v>3.5768109499999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="8" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L10" s="10">
+        <f>H10+J10</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="11" t="e">
+        <f t="shared" ref="M10:M11" si="5">L10*M$7/L$7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O10" s="17"/>
+      <c r="Z10" s="4">
+        <v>4226</v>
+      </c>
+      <c r="AA10" s="5">
+        <f t="shared" si="3"/>
+        <v>6.4869099999999999E-2</v>
+      </c>
+      <c r="AB10" s="7">
+        <v>13361</v>
+      </c>
+      <c r="AC10" s="8">
+        <f t="shared" si="4"/>
+        <v>0.20509135000000001</v>
+      </c>
+      <c r="AD10" s="10">
+        <f t="shared" si="0"/>
+        <v>17587</v>
+      </c>
+      <c r="AE10" s="12">
+        <f t="shared" ref="AE10:AE11" si="6">AD10*AE$7/AD$7</f>
+        <v>0.26996045000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="8" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L11" s="10">
+        <f>H11+J11</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="11" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>752</v>
+      </c>
+      <c r="AA11" s="5">
+        <f t="shared" si="3"/>
+        <v>1.1543199999999998E-2</v>
+      </c>
+      <c r="AB11" s="7">
+        <v>2005</v>
+      </c>
+      <c r="AC11" s="8">
+        <f t="shared" si="4"/>
+        <v>3.0776749999999999E-2</v>
+      </c>
+      <c r="AD11" s="10">
+        <f t="shared" si="0"/>
+        <v>2757</v>
+      </c>
+      <c r="AE11" s="12">
+        <f t="shared" si="6"/>
+        <v>4.2319949999999995E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="16"/>
+      <c r="Z12" s="4">
+        <v>395</v>
+      </c>
+      <c r="AA12" s="5">
+        <f>Z12*AE$7/AD$7</f>
+        <v>6.0632500000000001E-3</v>
+      </c>
+      <c r="AB12" s="7">
+        <v>1516</v>
+      </c>
+      <c r="AC12" s="8">
+        <f>AB12*AE$7/AD$7</f>
+        <v>2.3270599999999999E-2</v>
+      </c>
+      <c r="AD12" s="10">
+        <f t="shared" si="0"/>
+        <v>1911</v>
+      </c>
+      <c r="AE12" s="12">
+        <f>AD12*AE$7/AD$7</f>
+        <v>2.9333849999999998E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="16"/>
+      <c r="Z13" s="4">
+        <v>3843</v>
+      </c>
+      <c r="AA13" s="5">
+        <f>Z13*AE$7/AD$7</f>
+        <v>5.8990049999999995E-2</v>
+      </c>
+      <c r="AB13" s="7">
+        <v>13507</v>
+      </c>
+      <c r="AC13" s="8">
+        <f>AB13*AE$7/AD$7</f>
+        <v>0.20733244999999997</v>
+      </c>
+      <c r="AD13" s="10">
+        <f t="shared" si="0"/>
+        <v>17350</v>
+      </c>
+      <c r="AE13" s="12">
+        <f>AD13*AE$7/AD$7</f>
+        <v>0.26632250000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="23">
+        <v>240</v>
+      </c>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23">
+        <v>365</v>
+      </c>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="Y14" s="2"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="O15" s="2" t="e">
+        <f>D7/F7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P15" s="2" t="e">
+        <f>J7/L7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q15" s="1" t="str">
+        <f>A7</f>
+        <v>al</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="8" t="e">
+        <f t="shared" ref="E16:E21" si="7">D16*G$16/F$16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F16" s="10">
+        <f t="shared" ref="F16:F21" si="8">B16+D16</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="11">
+        <v>60.3</v>
+      </c>
+      <c r="H16" s="4">
+        <v>512726</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="7">
+        <v>4487274</v>
+      </c>
+      <c r="K16" s="8">
+        <f t="shared" ref="K16:K22" si="9">J16*M$16/L$16</f>
+        <v>24.105635928000002</v>
+      </c>
+      <c r="L16" s="10">
+        <f>H16+J16</f>
+        <v>5000000</v>
+      </c>
+      <c r="M16" s="11">
+        <v>26.86</v>
+      </c>
+      <c r="O16" s="2" t="e">
+        <f>D8/F8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P16" s="2" t="e">
+        <f>J8/L8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q16" s="1" t="str">
+        <f t="shared" ref="Q16:Q19" si="10">A8</f>
+        <v>gZ</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="8" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F17" s="10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="11" t="e">
+        <f>F17*G$16/F$16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H17" s="4">
+        <v>232904</v>
+      </c>
+      <c r="I17" s="5"/>
+      <c r="J17" s="7">
+        <v>3692990</v>
+      </c>
+      <c r="K17" s="8">
+        <f t="shared" si="9"/>
+        <v>19.838742279999998</v>
+      </c>
+      <c r="L17" s="10">
+        <f t="shared" ref="L16:L22" si="11">H17+J17</f>
+        <v>3925894</v>
+      </c>
+      <c r="M17" s="11">
+        <f t="shared" ref="M17:M22" si="12">L17*M$16/L$16</f>
+        <v>21.089902567999999</v>
+      </c>
+      <c r="P17" s="2" t="e">
+        <f t="shared" ref="P17:P19" si="13">J9/L9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q17" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>WW</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="8" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F18" s="10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="11" t="e">
+        <f>F18*G$16/F$16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H18" s="4">
+        <v>247158</v>
+      </c>
+      <c r="I18" s="5"/>
+      <c r="J18" s="7">
+        <v>704657</v>
+      </c>
+      <c r="K18" s="8">
+        <f t="shared" si="9"/>
+        <v>3.7854174039999999</v>
+      </c>
+      <c r="L18" s="10">
+        <f t="shared" si="11"/>
+        <v>951815</v>
+      </c>
+      <c r="M18" s="11">
+        <f t="shared" si="12"/>
+        <v>5.1131501799999999</v>
+      </c>
+      <c r="P18" s="2" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q18" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>ZZ</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="8" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F19" s="10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="11" t="e">
+        <f>F19*G$16/F$16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H19" s="4">
+        <v>19041</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="7">
+        <v>55485</v>
+      </c>
+      <c r="K19" s="8">
+        <f t="shared" si="9"/>
+        <v>0.29806541999999997</v>
+      </c>
+      <c r="L19" s="10">
+        <f t="shared" si="11"/>
+        <v>74526</v>
+      </c>
+      <c r="M19" s="11">
+        <f t="shared" si="12"/>
+        <v>0.40035367199999999</v>
+      </c>
+      <c r="P19" s="2" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q19" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>HW</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F20" s="10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="11" t="e">
+        <f>F20*G$16/F$16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H20" s="4">
+        <v>1059</v>
+      </c>
+      <c r="I20" s="5"/>
+      <c r="J20" s="7">
+        <v>2566</v>
+      </c>
+      <c r="K20" s="8">
+        <f t="shared" si="9"/>
+        <v>1.3784551999999999E-2</v>
+      </c>
+      <c r="L20" s="10">
+        <f t="shared" si="11"/>
+        <v>3625</v>
+      </c>
+      <c r="M20" s="11">
+        <f t="shared" si="12"/>
+        <v>1.9473500000000001E-2</v>
+      </c>
+      <c r="O20" s="2" t="e">
+        <f>D16/F16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P20" s="2">
+        <f>J16/L16</f>
+        <v>0.8974548</v>
+      </c>
+      <c r="Q20" s="1" t="str">
+        <f>A16</f>
+        <v>al</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="8" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F21" s="10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="11" t="e">
+        <f>F21*G$16/F$16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H21" s="4">
+        <v>2269</v>
+      </c>
+      <c r="I21" s="5"/>
+      <c r="J21" s="7">
+        <v>7905</v>
+      </c>
+      <c r="K21" s="8">
+        <f t="shared" si="9"/>
+        <v>4.2465659999999995E-2</v>
+      </c>
+      <c r="L21" s="10">
+        <f t="shared" si="11"/>
+        <v>10174</v>
+      </c>
+      <c r="M21" s="11">
+        <f t="shared" si="12"/>
+        <v>5.4654728E-2</v>
+      </c>
+      <c r="O21" s="2" t="e">
+        <f>D17/F17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P21" s="2">
+        <f>J17/L17</f>
+        <v>0.94067491379033663</v>
+      </c>
+      <c r="Q21" s="1" t="str">
+        <f t="shared" ref="Q21:Q26" si="14">A17</f>
+        <v>gZ</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="15"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="4">
+        <v>10295</v>
+      </c>
+      <c r="I22" s="5"/>
+      <c r="J22" s="7">
+        <v>23671</v>
+      </c>
+      <c r="K22" s="8">
+        <f t="shared" si="9"/>
+        <v>0.12716061199999998</v>
+      </c>
+      <c r="L22" s="10">
+        <f t="shared" si="11"/>
+        <v>33966</v>
+      </c>
+      <c r="M22" s="11">
+        <f t="shared" si="12"/>
+        <v>0.182465352</v>
+      </c>
+      <c r="O22" s="2" t="e">
+        <f t="shared" ref="O22:O25" si="15">D18/F18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P22" s="2">
+        <f t="shared" ref="P22:P25" si="16">J18/L18</f>
+        <v>0.74032979097828888</v>
+      </c>
+      <c r="Q22" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>WW</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O23" s="2" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P23" s="2">
+        <f t="shared" si="16"/>
+        <v>0.74450527332742933</v>
+      </c>
+      <c r="Q23" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>ZZ</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O24" s="2" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P24" s="2">
+        <f t="shared" si="16"/>
+        <v>0.70786206896551729</v>
+      </c>
+      <c r="Q24" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>HW</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O25" s="2" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P25" s="2">
+        <f t="shared" si="16"/>
+        <v>0.77698053862787497</v>
+      </c>
+      <c r="Q25" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>HZ</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O26" s="2"/>
+      <c r="P26" s="2">
+        <f>J22/L22</f>
+        <v>0.69690278513807924</v>
+      </c>
+      <c r="Q26" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>tt</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+    </row>
+    <row r="35" spans="13:20" x14ac:dyDescent="0.25">
+      <c r="P35" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>160</v>
+      </c>
+      <c r="R35" s="1">
+        <v>240</v>
+      </c>
+      <c r="S35" s="1">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="36" spans="13:20" x14ac:dyDescent="0.25">
+      <c r="O36" s="1">
+        <v>100</v>
+      </c>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="19"/>
+      <c r="S36" s="19"/>
+      <c r="T36" s="17"/>
+    </row>
+    <row r="37" spans="13:20" x14ac:dyDescent="0.25">
+      <c r="O37" s="1">
+        <v>95</v>
+      </c>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="19"/>
+      <c r="S37" s="19"/>
+      <c r="T37" s="17"/>
+    </row>
+    <row r="38" spans="13:20" x14ac:dyDescent="0.25">
+      <c r="O38" s="1">
+        <v>90</v>
+      </c>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="19"/>
+      <c r="R38" s="19"/>
+      <c r="S38" s="19"/>
+      <c r="T38" s="17"/>
+    </row>
+    <row r="39" spans="13:20" x14ac:dyDescent="0.25">
+      <c r="O39" s="1">
+        <v>85</v>
+      </c>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="19"/>
+      <c r="R39" s="19"/>
+      <c r="S39" s="19"/>
+      <c r="T39" s="17"/>
+    </row>
+    <row r="45" spans="13:20" x14ac:dyDescent="0.25">
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1593,6 +2669,320 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21627B4D-21E7-42EF-8EC8-F56129B85988}">
+  <dimension ref="A2:N41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="9.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="1"/>
+    <col min="11" max="11" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="1"/>
+    <col min="13" max="14" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="23">
+        <v>91.2</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23">
+        <v>160</v>
+      </c>
+      <c r="E2" s="23"/>
+      <c r="F2" s="18">
+        <v>240</v>
+      </c>
+      <c r="G2" s="18">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="8" t="e">
+        <f>#REF!*#REF!/C3</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C3" s="20">
+        <v>5000000</v>
+      </c>
+      <c r="D3" s="21" t="e">
+        <f>#REF!*#REF!/E$3</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E3" s="20">
+        <v>5000000</v>
+      </c>
+      <c r="F3" s="20">
+        <v>5000000</v>
+      </c>
+      <c r="G3" s="20">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="e">
+        <f>#REF!*#REF!/C4</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C4" s="20">
+        <v>5000000</v>
+      </c>
+      <c r="D4" s="21" t="e">
+        <f>#REF!*#REF!/E$3</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E4" s="20">
+        <v>4799181</v>
+      </c>
+      <c r="F4" s="20">
+        <v>3068124</v>
+      </c>
+      <c r="G4" s="20">
+        <v>2435489</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="8" t="e">
+        <f>#REF!*#REF!/E$3</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E5" s="20">
+        <v>176856</v>
+      </c>
+      <c r="F5" s="20">
+        <v>1758070</v>
+      </c>
+      <c r="G5" s="20">
+        <v>2248478</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="8" t="e">
+        <f>#REF!*#REF!/E$3</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E6" s="20">
+        <v>23954</v>
+      </c>
+      <c r="F6" s="20">
+        <v>149779</v>
+      </c>
+      <c r="G6" s="20">
+        <v>174812</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="8" t="e">
+        <f>#REF!*#REF!/E$3</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E7" s="20">
+        <v>9</v>
+      </c>
+      <c r="F7" s="20">
+        <v>1034</v>
+      </c>
+      <c r="G7" s="20">
+        <v>10052</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="20">
+        <v>22993</v>
+      </c>
+      <c r="G8" s="20">
+        <v>23717</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="20">
+        <v>107452</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C10" s="22">
+        <f>SUM(C4:C9)</f>
+        <v>5000000</v>
+      </c>
+      <c r="D10" s="22" t="e">
+        <f t="shared" ref="D10:G10" si="0">SUM(D4:D9)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E10" s="22">
+        <f t="shared" si="0"/>
+        <v>5000000</v>
+      </c>
+      <c r="F10" s="22">
+        <f t="shared" si="0"/>
+        <v>5000000</v>
+      </c>
+      <c r="G10" s="22">
+        <f t="shared" si="0"/>
+        <v>5000000</v>
+      </c>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C11" s="22">
+        <f>SUM(C5:C9)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="22" t="e">
+        <f t="shared" ref="D11:G11" si="1">SUM(D5:D9)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E11" s="22">
+        <f t="shared" si="1"/>
+        <v>200819</v>
+      </c>
+      <c r="F11" s="22">
+        <f t="shared" si="1"/>
+        <v>1931876</v>
+      </c>
+      <c r="G11" s="22">
+        <f t="shared" si="1"/>
+        <v>2564511</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C12" s="22">
+        <f>C4/C3*100</f>
+        <v>100</v>
+      </c>
+      <c r="D12" s="22" t="e">
+        <f t="shared" ref="D12:G12" si="2">D4/D3*100</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E12" s="22">
+        <f t="shared" si="2"/>
+        <v>95.983620000000002</v>
+      </c>
+      <c r="F12" s="22">
+        <f t="shared" si="2"/>
+        <v>61.362479999999998</v>
+      </c>
+      <c r="G12" s="22">
+        <f t="shared" si="2"/>
+        <v>48.709780000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F23" s="2"/>
+    </row>
+    <row r="32" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="17"/>
+    </row>
+    <row r="33" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="17"/>
+    </row>
+    <row r="34" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="17"/>
+    </row>
+    <row r="35" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="17"/>
+    </row>
+    <row r="41" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F41" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/7-TESLA_500G_Calibration/barns.xlsx
+++ b/7-TESLA_500G_Calibration/barns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmathew\cernbox\WINDOWS\Desktop\Git-Projects\HEP-Pheno-Project\7-TESLA_500G_Calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08712ACB-D1D8-4810-96E3-FFA63521C0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271C7E38-7686-4835-8B75-F5F3FF3294B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10785" yWindow="3570" windowWidth="12360" windowHeight="15375" activeTab="1" xr2:uid="{7960ABCD-F717-4580-A97E-BFEE89018374}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="1" xr2:uid="{7960ABCD-F717-4580-A97E-BFEE89018374}"/>
   </bookViews>
   <sheets>
     <sheet name="ISR_ON_1M" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="17">
   <si>
     <t>al</t>
   </si>
@@ -83,6 +83,12 @@
   </si>
   <si>
     <t>Non+Rad</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Survival</t>
   </si>
 </sst>
 </file>
@@ -179,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -237,6 +243,21 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -662,30 +683,30 @@
       <c r="A5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="28">
         <v>91.2</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23">
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28">
         <v>160</v>
       </c>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="Z5" s="23">
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="Z5" s="28">
         <v>500</v>
       </c>
-      <c r="AA5" s="23"/>
-      <c r="AB5" s="23"/>
-      <c r="AC5" s="23"/>
-      <c r="AD5" s="23"/>
-      <c r="AE5" s="23"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -1113,22 +1134,22 @@
       <c r="A14" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="28">
         <v>240</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23">
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28">
         <v>365</v>
       </c>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
       <c r="Y14" s="2"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
@@ -1675,242 +1696,230 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8C8F55F-93F0-4A61-B4C8-B8A5CBE0D442}">
-  <dimension ref="A5:AE45"/>
+  <dimension ref="A5:W45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
-    <col min="4" max="4" width="9.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="5" width="9.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
     <col min="8" max="8" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.140625" style="1"/>
     <col min="10" max="10" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.140625" style="1"/>
     <col min="14" max="14" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.140625" style="1"/>
     <col min="16" max="16" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9.140625" style="1"/>
-    <col min="18" max="18" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" style="1"/>
-    <col min="20" max="20" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" style="1"/>
-    <col min="22" max="22" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" style="1"/>
-    <col min="24" max="25" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.140625" style="1"/>
-    <col min="28" max="28" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.140625" style="1"/>
-    <col min="30" max="31" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="18" max="18" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="28">
         <v>91.2</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23">
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28">
         <v>160</v>
       </c>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="Z5" s="23">
-        <v>500</v>
-      </c>
-      <c r="AA5" s="23"/>
-      <c r="AB5" s="23"/>
-      <c r="AC5" s="23"/>
-      <c r="AD5" s="23"/>
-      <c r="AE5" s="23"/>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="O5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="P5" s="28">
+        <v>91.2</v>
+      </c>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28">
+        <v>160</v>
+      </c>
+      <c r="S5" s="28"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="Z6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA6" s="3" t="s">
+      <c r="O6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="P6" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q6" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="R6" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="S6" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="AB6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD6" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE6" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8" t="e">
-        <f>D7*G7/F7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F7" s="10">
-        <f>B7+D7</f>
+      <c r="B7" s="23">
+        <v>2157879</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="23">
+        <v>2842121</v>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="F7" s="23">
+        <f>SUM(B7,D7)</f>
+        <v>5000000</v>
+      </c>
+      <c r="G7" s="24">
+        <v>30.39</v>
+      </c>
+      <c r="H7" s="23">
+        <v>372556</v>
+      </c>
+      <c r="I7" s="24"/>
+      <c r="J7" s="23">
+        <v>4627444</v>
+      </c>
+      <c r="K7" s="24">
+        <f>J7*M$7/L$7</f>
+        <v>140.95194424000002</v>
+      </c>
+      <c r="L7" s="23">
+        <f>H7+J7</f>
+        <v>5000000</v>
+      </c>
+      <c r="M7" s="24">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="O7" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="G7" s="11">
-        <v>30.39</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="8" t="e">
-        <f>J7*M$7/L$7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L7" s="10">
-        <f>H7+J7</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="11">
-        <v>152.4</v>
-      </c>
-      <c r="Z7" s="4">
-        <v>105018</v>
-      </c>
-      <c r="AA7" s="5">
-        <f>Z7*AE$7/AD$7</f>
-        <v>1.6120263000000001</v>
-      </c>
-      <c r="AB7" s="7">
-        <v>894982</v>
-      </c>
-      <c r="AC7" s="8">
-        <f>AB7*AE$7/AD$7</f>
-        <v>13.7379737</v>
-      </c>
-      <c r="AD7" s="10">
-        <f t="shared" ref="AD7:AD13" si="0">Z7+AB7</f>
-        <v>1000000</v>
-      </c>
-      <c r="AE7" s="11">
-        <v>15.35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="P7" s="23">
+        <f>SUM(P8:P13)</f>
+        <v>5000000</v>
+      </c>
+      <c r="Q7" s="24">
+        <v>41.4</v>
+      </c>
+      <c r="R7" s="23">
+        <f>SUM(R8:R13)</f>
+        <v>5000000</v>
+      </c>
+      <c r="S7" s="24">
+        <v>40.229999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8" t="e">
-        <f t="shared" ref="E8" si="1">D8*G8/F8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F8" s="10">
-        <f>B8+D8</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="11" t="e">
+      <c r="B8" s="23">
+        <v>2157879</v>
+      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="23">
+        <v>2842121</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="23">
+        <f>SUM(B8,D8)</f>
+        <v>5000000</v>
+      </c>
+      <c r="G8" s="24">
         <f>F8*G7/F7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="8" t="e">
-        <f t="shared" ref="K8:K11" si="2">J8*M$7/L$7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L8" s="10">
-        <f>H8+J8</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="11" t="e">
+        <v>30.39</v>
+      </c>
+      <c r="H8" s="23">
+        <v>356124</v>
+      </c>
+      <c r="I8" s="24"/>
+      <c r="J8" s="23">
+        <v>4603198</v>
+      </c>
+      <c r="K8" s="24">
+        <f t="shared" ref="K8:K11" si="0">J8*M$7/L$7</f>
+        <v>140.21341108000001</v>
+      </c>
+      <c r="L8" s="23">
+        <f t="shared" ref="L8:L11" si="1">H8+J8</f>
+        <v>4959322</v>
+      </c>
+      <c r="M8" s="24">
         <f>L8*M$7/L$7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O8" s="17"/>
-      <c r="Z8" s="4">
-        <v>39617</v>
-      </c>
-      <c r="AA8" s="5">
-        <f t="shared" ref="AA8:AA11" si="3">Z8*AE$7/AD$7</f>
-        <v>0.60812094999999999</v>
-      </c>
-      <c r="AB8" s="7">
-        <v>687761</v>
-      </c>
-      <c r="AC8" s="8">
-        <f t="shared" ref="AC8:AC11" si="4">AB8*AE$7/AD$7</f>
-        <v>10.557131349999999</v>
-      </c>
-      <c r="AD8" s="10">
-        <f t="shared" si="0"/>
-        <v>727378</v>
-      </c>
-      <c r="AE8" s="12">
-        <f>AD8*AE$7/AD$7</f>
-        <v>11.165252299999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+        <v>151.06094812000001</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="23">
+        <v>5000000</v>
+      </c>
+      <c r="Q8" s="24">
+        <f>P8*Q7/P7</f>
+        <v>41.4</v>
+      </c>
+      <c r="R8" s="23">
+        <v>4799181</v>
+      </c>
+      <c r="S8" s="24">
+        <f>R8*S7/R7</f>
+        <v>38.614210325999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>3</v>
       </c>
@@ -1920,45 +1929,39 @@
       <c r="E9" s="16"/>
       <c r="F9" s="15"/>
       <c r="G9" s="16"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="8" t="e">
+      <c r="H9" s="23">
+        <v>14336</v>
+      </c>
+      <c r="I9" s="24"/>
+      <c r="J9" s="23">
+        <v>20003</v>
+      </c>
+      <c r="K9" s="24">
         <f>J9*M$7/L$7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L9" s="10">
-        <f>H9+J9</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="11" t="e">
-        <f>L9*M$7/L$7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z9" s="4">
-        <v>56185</v>
-      </c>
-      <c r="AA9" s="5">
-        <f>Z9*AE$7/AD$7</f>
-        <v>0.86243974999999995</v>
-      </c>
-      <c r="AB9" s="7">
-        <v>176832</v>
-      </c>
-      <c r="AC9" s="8">
-        <f>AB9*AE$7/AD$7</f>
-        <v>2.7143711999999995</v>
-      </c>
-      <c r="AD9" s="10">
-        <f t="shared" si="0"/>
-        <v>233017</v>
-      </c>
-      <c r="AE9" s="12">
-        <f>AD9*AE$7/AD$7</f>
-        <v>3.5768109499999996</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0.60929138000000005</v>
+      </c>
+      <c r="L9" s="23">
+        <f t="shared" si="1"/>
+        <v>34339</v>
+      </c>
+      <c r="M9" s="24">
+        <f t="shared" ref="M9:M11" si="2">L9*M$7/L$7</f>
+        <v>1.0459659400000001</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="23">
+        <v>176856</v>
+      </c>
+      <c r="S9" s="24">
+        <f>R9*S7/R7</f>
+        <v>1.4229833759999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>2</v>
       </c>
@@ -1968,46 +1971,39 @@
       <c r="E10" s="16"/>
       <c r="F10" s="15"/>
       <c r="G10" s="16"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="8" t="e">
+      <c r="H10" s="23">
+        <v>2095</v>
+      </c>
+      <c r="I10" s="24"/>
+      <c r="J10" s="23">
+        <v>4241</v>
+      </c>
+      <c r="K10" s="24">
+        <f t="shared" si="0"/>
+        <v>0.12918086000000001</v>
+      </c>
+      <c r="L10" s="23">
+        <f t="shared" si="1"/>
+        <v>6336</v>
+      </c>
+      <c r="M10" s="24">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L10" s="10">
-        <f>H10+J10</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="11" t="e">
-        <f t="shared" ref="M10:M11" si="5">L10*M$7/L$7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O10" s="17"/>
-      <c r="Z10" s="4">
-        <v>4226</v>
-      </c>
-      <c r="AA10" s="5">
-        <f t="shared" si="3"/>
-        <v>6.4869099999999999E-2</v>
-      </c>
-      <c r="AB10" s="7">
-        <v>13361</v>
-      </c>
-      <c r="AC10" s="8">
-        <f t="shared" si="4"/>
-        <v>0.20509135000000001</v>
-      </c>
-      <c r="AD10" s="10">
-        <f t="shared" si="0"/>
-        <v>17587</v>
-      </c>
-      <c r="AE10" s="12">
-        <f t="shared" ref="AE10:AE11" si="6">AD10*AE$7/AD$7</f>
-        <v>0.26996045000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0.19299456000000001</v>
+      </c>
+      <c r="O10" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="23">
+        <v>23954</v>
+      </c>
+      <c r="S10" s="24">
+        <f>R10*S7/R7</f>
+        <v>0.19273388399999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>6</v>
       </c>
@@ -2017,45 +2013,39 @@
       <c r="E11" s="16"/>
       <c r="F11" s="15"/>
       <c r="G11" s="16"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="8" t="e">
+      <c r="H11" s="23">
+        <v>1</v>
+      </c>
+      <c r="I11" s="24"/>
+      <c r="J11" s="23">
+        <v>2</v>
+      </c>
+      <c r="K11" s="24">
+        <f t="shared" si="0"/>
+        <v>6.0920000000000006E-5</v>
+      </c>
+      <c r="L11" s="23">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="M11" s="24">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L11" s="10">
-        <f>H11+J11</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z11" s="4">
-        <v>752</v>
-      </c>
-      <c r="AA11" s="5">
-        <f t="shared" si="3"/>
-        <v>1.1543199999999998E-2</v>
-      </c>
-      <c r="AB11" s="7">
-        <v>2005</v>
-      </c>
-      <c r="AC11" s="8">
-        <f t="shared" si="4"/>
-        <v>3.0776749999999999E-2</v>
-      </c>
-      <c r="AD11" s="10">
-        <f t="shared" si="0"/>
-        <v>2757</v>
-      </c>
-      <c r="AE11" s="12">
-        <f t="shared" si="6"/>
-        <v>4.2319949999999995E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+        <v>9.1380000000000009E-5</v>
+      </c>
+      <c r="O11" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="23">
+        <v>9</v>
+      </c>
+      <c r="S11" s="24">
+        <f>R11*S7/R7</f>
+        <v>7.2414000000000002E-5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>5</v>
       </c>
@@ -2071,30 +2061,15 @@
       <c r="K12" s="16"/>
       <c r="L12" s="15"/>
       <c r="M12" s="16"/>
-      <c r="Z12" s="4">
-        <v>395</v>
-      </c>
-      <c r="AA12" s="5">
-        <f>Z12*AE$7/AD$7</f>
-        <v>6.0632500000000001E-3</v>
-      </c>
-      <c r="AB12" s="7">
-        <v>1516</v>
-      </c>
-      <c r="AC12" s="8">
-        <f>AB12*AE$7/AD$7</f>
-        <v>2.3270599999999999E-2</v>
-      </c>
-      <c r="AD12" s="10">
-        <f t="shared" si="0"/>
-        <v>1911</v>
-      </c>
-      <c r="AE12" s="12">
-        <f>AD12*AE$7/AD$7</f>
-        <v>2.9333849999999998E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="O12" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="16"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>4</v>
       </c>
@@ -2110,397 +2085,443 @@
       <c r="K13" s="16"/>
       <c r="L13" s="15"/>
       <c r="M13" s="16"/>
-      <c r="Z13" s="4">
-        <v>3843</v>
-      </c>
-      <c r="AA13" s="5">
-        <f>Z13*AE$7/AD$7</f>
-        <v>5.8990049999999995E-2</v>
-      </c>
-      <c r="AB13" s="7">
-        <v>13507</v>
-      </c>
-      <c r="AC13" s="8">
-        <f>AB13*AE$7/AD$7</f>
-        <v>0.20733244999999997</v>
-      </c>
-      <c r="AD13" s="10">
-        <f t="shared" si="0"/>
-        <v>17350</v>
-      </c>
-      <c r="AE13" s="12">
-        <f>AD13*AE$7/AD$7</f>
-        <v>0.26632250000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="O13" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="16"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="28">
         <v>240</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23">
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28">
         <v>365</v>
       </c>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="Y14" s="2"/>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="O14" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="P14" s="28">
+        <v>240</v>
+      </c>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28">
+        <v>365</v>
+      </c>
+      <c r="S14" s="28"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="M15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="O15" s="2" t="e">
-        <f>D7/F7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P15" s="2" t="e">
-        <f>J7/L7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q15" s="1" t="str">
-        <f>A7</f>
-        <v>al</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="O15" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q15" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="R15" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="S15" s="25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8" t="e">
-        <f t="shared" ref="E16:E21" si="7">D16*G$16/F$16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F16" s="10">
-        <f t="shared" ref="F16:F21" si="8">B16+D16</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="11">
+      <c r="B16" s="23">
+        <v>484097</v>
+      </c>
+      <c r="C16" s="24"/>
+      <c r="D16" s="23">
+        <v>4515903</v>
+      </c>
+      <c r="E16" s="24"/>
+      <c r="F16" s="23">
+        <f>SUM(B16,D16)</f>
+        <v>5000000</v>
+      </c>
+      <c r="G16" s="24">
         <v>60.3</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="23">
         <v>512726</v>
       </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="7">
+      <c r="I16" s="24"/>
+      <c r="J16" s="23">
         <v>4487274</v>
       </c>
-      <c r="K16" s="8">
-        <f t="shared" ref="K16:K22" si="9">J16*M$16/L$16</f>
+      <c r="K16" s="24">
+        <f t="shared" ref="K16:K22" si="3">J16*M$16/L$16</f>
         <v>24.105635928000002</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="23">
         <f>H16+J16</f>
         <v>5000000</v>
       </c>
-      <c r="M16" s="11">
+      <c r="M16" s="24">
         <v>26.86</v>
       </c>
-      <c r="O16" s="2" t="e">
-        <f>D8/F8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P16" s="2" t="e">
-        <f>J8/L8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q16" s="1" t="str">
-        <f t="shared" ref="Q16:Q19" si="10">A8</f>
-        <v>gZ</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O16" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P16" s="23">
+        <f>SUM(P17:P22)</f>
+        <v>5000000</v>
+      </c>
+      <c r="Q16" s="24">
+        <v>21.82</v>
+      </c>
+      <c r="R16" s="23">
+        <f>SUM(R17:R22)</f>
+        <v>5000000</v>
+      </c>
+      <c r="S16" s="24">
+        <v>11.01</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F17" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="11" t="e">
+      <c r="B17" s="23">
+        <v>285570</v>
+      </c>
+      <c r="C17" s="24"/>
+      <c r="D17" s="23">
+        <v>4034478</v>
+      </c>
+      <c r="E17" s="24"/>
+      <c r="F17" s="23">
+        <f t="shared" ref="F17:F21" si="4">SUM(B17,D17)</f>
+        <v>4320048</v>
+      </c>
+      <c r="G17" s="24">
         <f>F17*G$16/F$16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H17" s="4">
+        <v>52.099778879999995</v>
+      </c>
+      <c r="H17" s="23">
         <v>232904</v>
       </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="7">
+      <c r="I17" s="24"/>
+      <c r="J17" s="23">
         <v>3692990</v>
       </c>
-      <c r="K17" s="8">
-        <f t="shared" si="9"/>
+      <c r="K17" s="24">
+        <f t="shared" si="3"/>
         <v>19.838742279999998</v>
       </c>
-      <c r="L17" s="10">
-        <f t="shared" ref="L16:L22" si="11">H17+J17</f>
+      <c r="L17" s="23">
+        <f t="shared" ref="L17:L22" si="5">H17+J17</f>
         <v>3925894</v>
       </c>
-      <c r="M17" s="11">
-        <f t="shared" ref="M17:M22" si="12">L17*M$16/L$16</f>
+      <c r="M17" s="24">
+        <f t="shared" ref="M17:M22" si="6">L17*M$16/L$16</f>
         <v>21.089902567999999</v>
       </c>
-      <c r="P17" s="2" t="e">
-        <f t="shared" ref="P17:P19" si="13">J9/L9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q17" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>WW</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O17" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="P17" s="23">
+        <v>3068124</v>
+      </c>
+      <c r="Q17" s="24">
+        <f>P17*$Q$16/$P$16</f>
+        <v>13.389293135999999</v>
+      </c>
+      <c r="R17" s="23">
+        <v>2435489</v>
+      </c>
+      <c r="S17" s="24">
+        <f>R17*$S$16/$R$16</f>
+        <v>5.3629467780000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F18" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="11" t="e">
-        <f>F18*G$16/F$16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H18" s="4">
+      <c r="B18" s="23">
+        <v>180684</v>
+      </c>
+      <c r="C18" s="24"/>
+      <c r="D18" s="23">
+        <v>439103</v>
+      </c>
+      <c r="E18" s="24"/>
+      <c r="F18" s="23">
+        <f t="shared" si="4"/>
+        <v>619787</v>
+      </c>
+      <c r="G18" s="24">
+        <f t="shared" ref="G18:G21" si="7">F18*G$16/F$16</f>
+        <v>7.47463122</v>
+      </c>
+      <c r="H18" s="23">
         <v>247158</v>
       </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="7">
+      <c r="I18" s="24"/>
+      <c r="J18" s="23">
         <v>704657</v>
       </c>
-      <c r="K18" s="8">
-        <f t="shared" si="9"/>
+      <c r="K18" s="24">
+        <f t="shared" si="3"/>
         <v>3.7854174039999999</v>
       </c>
-      <c r="L18" s="10">
-        <f t="shared" si="11"/>
+      <c r="L18" s="23">
+        <f t="shared" si="5"/>
         <v>951815</v>
       </c>
-      <c r="M18" s="11">
-        <f t="shared" si="12"/>
+      <c r="M18" s="24">
+        <f t="shared" si="6"/>
         <v>5.1131501799999999</v>
       </c>
-      <c r="P18" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q18" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>ZZ</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O18" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="23">
+        <v>1758070</v>
+      </c>
+      <c r="Q18" s="24">
+        <f t="shared" ref="Q18:Q21" si="8">P18*$Q$16/$P$16</f>
+        <v>7.6722174799999996</v>
+      </c>
+      <c r="R18" s="23">
+        <v>2248478</v>
+      </c>
+      <c r="S18" s="24">
+        <f t="shared" ref="S18:S22" si="9">R18*$S$16/$R$16</f>
+        <v>4.9511485560000006</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8" t="e">
+      <c r="B19" s="23">
+        <v>15619</v>
+      </c>
+      <c r="C19" s="24"/>
+      <c r="D19" s="23">
+        <v>37118</v>
+      </c>
+      <c r="E19" s="24"/>
+      <c r="F19" s="23">
+        <f t="shared" si="4"/>
+        <v>52737</v>
+      </c>
+      <c r="G19" s="24">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F19" s="10">
+        <v>0.6360082199999999</v>
+      </c>
+      <c r="H19" s="23">
+        <v>19041</v>
+      </c>
+      <c r="I19" s="24"/>
+      <c r="J19" s="23">
+        <v>55485</v>
+      </c>
+      <c r="K19" s="24">
+        <f t="shared" si="3"/>
+        <v>0.29806541999999997</v>
+      </c>
+      <c r="L19" s="23">
+        <f t="shared" si="5"/>
+        <v>74526</v>
+      </c>
+      <c r="M19" s="24">
+        <f t="shared" si="6"/>
+        <v>0.40035367199999999</v>
+      </c>
+      <c r="O19" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="P19" s="23">
+        <v>149779</v>
+      </c>
+      <c r="Q19" s="24">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="11" t="e">
-        <f>F19*G$16/F$16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H19" s="4">
-        <v>19041</v>
-      </c>
-      <c r="I19" s="5"/>
-      <c r="J19" s="7">
-        <v>55485</v>
-      </c>
-      <c r="K19" s="8">
+        <v>0.65363555600000001</v>
+      </c>
+      <c r="R19" s="23">
+        <v>174812</v>
+      </c>
+      <c r="S19" s="24">
         <f t="shared" si="9"/>
-        <v>0.29806541999999997</v>
-      </c>
-      <c r="L19" s="10">
-        <f t="shared" si="11"/>
-        <v>74526</v>
-      </c>
-      <c r="M19" s="11">
-        <f t="shared" si="12"/>
-        <v>0.40035367199999999</v>
-      </c>
-      <c r="P19" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q19" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>HW</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.38493602399999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8" t="e">
+      <c r="B20" s="23">
+        <v>87</v>
+      </c>
+      <c r="C20" s="24"/>
+      <c r="D20" s="23">
+        <v>205</v>
+      </c>
+      <c r="E20" s="24"/>
+      <c r="F20" s="23">
+        <f t="shared" si="4"/>
+        <v>292</v>
+      </c>
+      <c r="G20" s="24">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F20" s="10">
+        <v>3.5215199999999998E-3</v>
+      </c>
+      <c r="H20" s="23">
+        <v>1059</v>
+      </c>
+      <c r="I20" s="24"/>
+      <c r="J20" s="23">
+        <v>2566</v>
+      </c>
+      <c r="K20" s="24">
+        <f t="shared" si="3"/>
+        <v>1.3784551999999999E-2</v>
+      </c>
+      <c r="L20" s="23">
+        <f t="shared" si="5"/>
+        <v>3625</v>
+      </c>
+      <c r="M20" s="24">
+        <f t="shared" si="6"/>
+        <v>1.9473500000000001E-2</v>
+      </c>
+      <c r="O20" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="P20" s="23">
+        <v>1034</v>
+      </c>
+      <c r="Q20" s="24">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="11" t="e">
-        <f>F20*G$16/F$16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H20" s="4">
-        <v>1059</v>
-      </c>
-      <c r="I20" s="5"/>
-      <c r="J20" s="7">
-        <v>2566</v>
-      </c>
-      <c r="K20" s="8">
+        <v>4.5123760000000002E-3</v>
+      </c>
+      <c r="R20" s="23">
+        <v>10052</v>
+      </c>
+      <c r="S20" s="24">
         <f t="shared" si="9"/>
-        <v>1.3784551999999999E-2</v>
-      </c>
-      <c r="L20" s="10">
-        <f t="shared" si="11"/>
-        <v>3625</v>
-      </c>
-      <c r="M20" s="11">
-        <f t="shared" si="12"/>
-        <v>1.9473500000000001E-2</v>
-      </c>
-      <c r="O20" s="2" t="e">
-        <f>D16/F16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P20" s="2">
-        <f>J16/L16</f>
-        <v>0.8974548</v>
-      </c>
-      <c r="Q20" s="1" t="str">
-        <f>A16</f>
-        <v>al</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+        <v>2.2134503999999999E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8" t="e">
+      <c r="B21" s="23">
+        <v>2137</v>
+      </c>
+      <c r="C21" s="24"/>
+      <c r="D21" s="23">
+        <v>4999</v>
+      </c>
+      <c r="E21" s="24"/>
+      <c r="F21" s="23">
+        <f t="shared" si="4"/>
+        <v>7136</v>
+      </c>
+      <c r="G21" s="24">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F21" s="10">
+        <v>8.6060159999999997E-2</v>
+      </c>
+      <c r="H21" s="23">
+        <v>2269</v>
+      </c>
+      <c r="I21" s="24"/>
+      <c r="J21" s="23">
+        <v>7905</v>
+      </c>
+      <c r="K21" s="24">
+        <f t="shared" si="3"/>
+        <v>4.2465659999999995E-2</v>
+      </c>
+      <c r="L21" s="23">
+        <f t="shared" si="5"/>
+        <v>10174</v>
+      </c>
+      <c r="M21" s="24">
+        <f t="shared" si="6"/>
+        <v>5.4654728E-2</v>
+      </c>
+      <c r="O21" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="23">
+        <v>22993</v>
+      </c>
+      <c r="Q21" s="24">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="11" t="e">
-        <f>F21*G$16/F$16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H21" s="4">
-        <v>2269</v>
-      </c>
-      <c r="I21" s="5"/>
-      <c r="J21" s="7">
-        <v>7905</v>
-      </c>
-      <c r="K21" s="8">
+        <v>0.100341452</v>
+      </c>
+      <c r="R21" s="23">
+        <v>23717</v>
+      </c>
+      <c r="S21" s="24">
         <f t="shared" si="9"/>
-        <v>4.2465659999999995E-2</v>
-      </c>
-      <c r="L21" s="10">
-        <f t="shared" si="11"/>
-        <v>10174</v>
-      </c>
-      <c r="M21" s="11">
-        <f t="shared" si="12"/>
-        <v>5.4654728E-2</v>
-      </c>
-      <c r="O21" s="2" t="e">
-        <f>D17/F17</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P21" s="2">
-        <f>J17/L17</f>
-        <v>0.94067491379033663</v>
-      </c>
-      <c r="Q21" s="1" t="str">
-        <f t="shared" ref="Q21:Q26" si="14">A17</f>
-        <v>gZ</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5.2224833999999998E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>4</v>
       </c>
@@ -2510,162 +2531,340 @@
       <c r="E22" s="16"/>
       <c r="F22" s="15"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="4">
+      <c r="H22" s="23">
         <v>10295</v>
       </c>
-      <c r="I22" s="5"/>
-      <c r="J22" s="7">
+      <c r="I22" s="24"/>
+      <c r="J22" s="23">
         <v>23671</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="24">
+        <f t="shared" si="3"/>
+        <v>0.12716061199999998</v>
+      </c>
+      <c r="L22" s="23">
+        <f t="shared" si="5"/>
+        <v>33966</v>
+      </c>
+      <c r="M22" s="24">
+        <f t="shared" si="6"/>
+        <v>0.182465352</v>
+      </c>
+      <c r="O22" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="23">
+        <v>107452</v>
+      </c>
+      <c r="S22" s="24">
         <f t="shared" si="9"/>
-        <v>0.12716061199999998</v>
-      </c>
-      <c r="L22" s="10">
-        <f t="shared" si="11"/>
-        <v>33966</v>
-      </c>
-      <c r="M22" s="11">
-        <f t="shared" si="12"/>
-        <v>0.182465352</v>
-      </c>
-      <c r="O22" s="2" t="e">
-        <f t="shared" ref="O22:O25" si="15">D18/F18</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P22" s="2">
-        <f t="shared" ref="P22:P25" si="16">J18/L18</f>
-        <v>0.74032979097828888</v>
-      </c>
-      <c r="Q22" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>WW</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O23" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P23" s="2">
-        <f t="shared" si="16"/>
-        <v>0.74450527332742933</v>
-      </c>
-      <c r="Q23" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>ZZ</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O24" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P24" s="2">
-        <f t="shared" si="16"/>
-        <v>0.70786206896551729</v>
-      </c>
-      <c r="Q24" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>HW</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O25" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P25" s="2">
-        <f t="shared" si="16"/>
-        <v>0.77698053862787497</v>
-      </c>
-      <c r="Q25" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>HZ</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O26" s="2"/>
-      <c r="P26" s="2">
-        <f>J22/L22</f>
-        <v>0.69690278513807924</v>
-      </c>
-      <c r="Q26" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>tt</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-    </row>
-    <row r="35" spans="13:20" x14ac:dyDescent="0.25">
-      <c r="P35" s="1">
+        <v>0.23660930399999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O25" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="P25" s="26">
         <v>91.2</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q25" s="26">
         <v>160</v>
       </c>
-      <c r="R35" s="1">
+      <c r="R25" s="26">
         <v>240</v>
       </c>
-      <c r="S35" s="1">
+      <c r="S25" s="26">
         <v>365</v>
       </c>
-    </row>
-    <row r="36" spans="13:20" x14ac:dyDescent="0.25">
-      <c r="O36" s="1">
+      <c r="T25" s="26">
+        <v>91.2</v>
+      </c>
+      <c r="U25" s="26">
+        <v>160</v>
+      </c>
+      <c r="V25" s="26">
+        <v>240</v>
+      </c>
+      <c r="W25" s="26">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O26" s="26">
         <v>100</v>
       </c>
+      <c r="P26" s="26">
+        <v>2157879</v>
+      </c>
+      <c r="Q26" s="26">
+        <v>356124</v>
+      </c>
+      <c r="R26" s="26">
+        <v>285570</v>
+      </c>
+      <c r="S26" s="26">
+        <v>232904</v>
+      </c>
+      <c r="T26" s="1">
+        <f>$O$30-P26</f>
+        <v>2842121</v>
+      </c>
+      <c r="U26" s="1">
+        <f>$O$30-Q26</f>
+        <v>4643876</v>
+      </c>
+      <c r="V26" s="1">
+        <f>$O$30-R26</f>
+        <v>4714430</v>
+      </c>
+      <c r="W26" s="1">
+        <f>$O$30-S26</f>
+        <v>4767096</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O27" s="26">
+        <v>95</v>
+      </c>
+      <c r="P27" s="26">
+        <v>4988808</v>
+      </c>
+      <c r="Q27" s="26">
+        <v>2798396</v>
+      </c>
+      <c r="R27" s="26">
+        <v>2495242</v>
+      </c>
+      <c r="S27" s="26">
+        <v>2316404</v>
+      </c>
+      <c r="T27" s="1">
+        <f>$O$30-P27</f>
+        <v>11192</v>
+      </c>
+      <c r="U27" s="1">
+        <f>$O$30-Q27</f>
+        <v>2201604</v>
+      </c>
+      <c r="V27" s="1">
+        <f>$O$30-R27</f>
+        <v>2504758</v>
+      </c>
+      <c r="W27" s="1">
+        <f>$O$30-S27</f>
+        <v>2683596</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O28" s="26">
+        <v>90</v>
+      </c>
+      <c r="P28" s="26">
+        <v>4996726</v>
+      </c>
+      <c r="Q28" s="26">
+        <v>2952700</v>
+      </c>
+      <c r="R28" s="26">
+        <v>2620116</v>
+      </c>
+      <c r="S28" s="26">
+        <v>2426752</v>
+      </c>
+      <c r="T28" s="1">
+        <f>$O$30-P28</f>
+        <v>3274</v>
+      </c>
+      <c r="U28" s="1">
+        <f>$O$30-Q28</f>
+        <v>2047300</v>
+      </c>
+      <c r="V28" s="1">
+        <f>$O$30-R28</f>
+        <v>2379884</v>
+      </c>
+      <c r="W28" s="1">
+        <f>$O$30-S28</f>
+        <v>2573248</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O29" s="26">
+        <v>85</v>
+      </c>
+      <c r="P29" s="26">
+        <v>4998079</v>
+      </c>
+      <c r="Q29" s="26">
+        <v>3048128</v>
+      </c>
+      <c r="R29" s="26">
+        <v>2692550</v>
+      </c>
+      <c r="S29" s="26">
+        <v>2489559</v>
+      </c>
+      <c r="T29" s="1">
+        <f>$O$30-P29</f>
+        <v>1921</v>
+      </c>
+      <c r="U29" s="1">
+        <f>$O$30-Q29</f>
+        <v>1951872</v>
+      </c>
+      <c r="V29" s="1">
+        <f>$O$30-R29</f>
+        <v>2307450</v>
+      </c>
+      <c r="W29" s="1">
+        <f>$O$30-S29</f>
+        <v>2510441</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O30" s="26">
+        <v>5000000</v>
+      </c>
+      <c r="P30" s="26">
+        <v>91.2</v>
+      </c>
+      <c r="Q30" s="26">
+        <v>160</v>
+      </c>
+      <c r="R30" s="26">
+        <v>240</v>
+      </c>
+      <c r="S30" s="26">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O31" s="26">
+        <v>100</v>
+      </c>
+      <c r="P31" s="27">
+        <f>P26/$O$30*100</f>
+        <v>43.157580000000003</v>
+      </c>
+      <c r="Q31" s="27">
+        <f>Q26/$O$30*100</f>
+        <v>7.1224800000000004</v>
+      </c>
+      <c r="R31" s="27">
+        <f>R26/$O$30*100</f>
+        <v>5.7113999999999994</v>
+      </c>
+      <c r="S31" s="27">
+        <f>S26/$O$30*100</f>
+        <v>4.65808</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O32" s="26">
+        <v>95</v>
+      </c>
+      <c r="P32" s="27">
+        <f>P27/$O$30*100</f>
+        <v>99.776160000000004</v>
+      </c>
+      <c r="Q32" s="27">
+        <f>Q27/$O$30*100</f>
+        <v>55.967920000000007</v>
+      </c>
+      <c r="R32" s="27">
+        <f>R27/$O$30*100</f>
+        <v>49.90484</v>
+      </c>
+      <c r="S32" s="27">
+        <f>S27/$O$30*100</f>
+        <v>46.32808</v>
+      </c>
+    </row>
+    <row r="33" spans="13:19" x14ac:dyDescent="0.25">
+      <c r="O33" s="26">
+        <v>90</v>
+      </c>
+      <c r="P33" s="27">
+        <f>P28/$O$30*100</f>
+        <v>99.934520000000006</v>
+      </c>
+      <c r="Q33" s="27">
+        <f>Q28/$O$30*100</f>
+        <v>59.053999999999995</v>
+      </c>
+      <c r="R33" s="27">
+        <f>R28/$O$30*100</f>
+        <v>52.402320000000003</v>
+      </c>
+      <c r="S33" s="27">
+        <f>S28/$O$30*100</f>
+        <v>48.535040000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="13:19" x14ac:dyDescent="0.25">
+      <c r="O34" s="26">
+        <v>85</v>
+      </c>
+      <c r="P34" s="27">
+        <f>P29/$O$30*100</f>
+        <v>99.961580000000012</v>
+      </c>
+      <c r="Q34" s="27">
+        <f>Q29/$O$30*100</f>
+        <v>60.962559999999996</v>
+      </c>
+      <c r="R34" s="27">
+        <f>R29/$O$30*100</f>
+        <v>53.851000000000006</v>
+      </c>
+      <c r="S34" s="27">
+        <f>S29/$O$30*100</f>
+        <v>49.791180000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="13:19" x14ac:dyDescent="0.25">
       <c r="P36" s="19"/>
       <c r="Q36" s="19"/>
-      <c r="R36" s="19"/>
-      <c r="S36" s="19"/>
-      <c r="T36" s="17"/>
-    </row>
-    <row r="37" spans="13:20" x14ac:dyDescent="0.25">
-      <c r="O37" s="1">
-        <v>95</v>
-      </c>
+    </row>
+    <row r="37" spans="13:19" x14ac:dyDescent="0.25">
       <c r="P37" s="19"/>
       <c r="Q37" s="19"/>
-      <c r="R37" s="19"/>
-      <c r="S37" s="19"/>
-      <c r="T37" s="17"/>
-    </row>
-    <row r="38" spans="13:20" x14ac:dyDescent="0.25">
-      <c r="O38" s="1">
-        <v>90</v>
-      </c>
+    </row>
+    <row r="38" spans="13:19" x14ac:dyDescent="0.25">
       <c r="P38" s="19"/>
       <c r="Q38" s="19"/>
-      <c r="R38" s="19"/>
-      <c r="S38" s="19"/>
-      <c r="T38" s="17"/>
-    </row>
-    <row r="39" spans="13:20" x14ac:dyDescent="0.25">
-      <c r="O39" s="1">
-        <v>85</v>
-      </c>
+    </row>
+    <row r="39" spans="13:19" x14ac:dyDescent="0.25">
       <c r="P39" s="19"/>
       <c r="Q39" s="19"/>
-      <c r="R39" s="19"/>
-      <c r="S39" s="19"/>
-      <c r="T39" s="17"/>
-    </row>
-    <row r="45" spans="13:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="13:19" x14ac:dyDescent="0.25">
       <c r="M45" s="17"/>
       <c r="N45" s="17"/>
       <c r="O45" s="17"/>
       <c r="P45" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R14:S14"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="H5:M5"/>
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="H14:M14"/>
-    <mergeCell ref="Z5:AE5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -2697,14 +2896,14 @@
       <c r="A2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="28">
         <v>91.2</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28">
         <v>160</v>
       </c>
-      <c r="E2" s="23"/>
+      <c r="E2" s="28"/>
       <c r="F2" s="18">
         <v>240</v>
       </c>
